--- a/template.xlsx
+++ b/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\1. Work\1. Daily\Capacity Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38BDFB9D-3AD6-4D0F-B8D9-A4AF144AED36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08585676-006E-4F97-9BE7-218C847D9F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="810" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -688,7 +688,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -757,11 +757,7 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="7" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="4" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -782,6 +778,8 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="4" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1103,18 +1101,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="57" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
+      <c r="A1" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
       <c r="K1" s="5"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1142,24 +1140,24 @@
       <c r="R2" s="17"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="63" t="s">
+      <c r="B3" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="59" t="s">
+      <c r="C3" s="55" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="62" t="s">
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="58" t="s">
         <v>119</v>
       </c>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="61"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="57"/>
       <c r="K3" s="5"/>
       <c r="L3" s="18" t="s">
         <v>5</v>
@@ -1184,15 +1182,15 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="64"/>
-      <c r="B4" s="64"/>
+      <c r="A4" s="60"/>
+      <c r="B4" s="60"/>
       <c r="C4" s="50">
         <f ca="1">TODAY()</f>
-        <v>46113</v>
+        <v>46117</v>
       </c>
       <c r="D4" s="50">
         <f ca="1">C4-1</f>
-        <v>46112</v>
+        <v>46116</v>
       </c>
       <c r="E4" s="51" t="s">
         <v>12</v>
@@ -1202,11 +1200,11 @@
       </c>
       <c r="G4" s="50">
         <f ca="1">TODAY()</f>
-        <v>46113</v>
+        <v>46117</v>
       </c>
       <c r="H4" s="50">
         <f ca="1">G4-1</f>
-        <v>46112</v>
+        <v>46116</v>
       </c>
       <c r="I4" s="51" t="s">
         <v>12</v>
@@ -1236,31 +1234,31 @@
       <c r="B5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="53">
-        <v>-513</v>
-      </c>
-      <c r="D5" s="53">
-        <v>-1062</v>
-      </c>
-      <c r="E5" s="53">
-        <v>-549</v>
-      </c>
-      <c r="F5" s="10">
+      <c r="C5" s="63">
+        <v>77</v>
+      </c>
+      <c r="D5" s="63">
+        <v>221</v>
+      </c>
+      <c r="E5" s="63">
+        <v>144</v>
+      </c>
+      <c r="F5" s="7">
         <f>C5/C60</f>
-        <v>-0.34803256445047492</v>
-      </c>
-      <c r="G5" s="54">
-        <v>622</v>
-      </c>
-      <c r="H5" s="54">
-        <v>739</v>
-      </c>
-      <c r="I5" s="54">
-        <v>117</v>
+        <v>5.2238805970149252E-2</v>
+      </c>
+      <c r="G5" s="63">
+        <v>1624</v>
+      </c>
+      <c r="H5" s="63">
+        <v>1627</v>
+      </c>
+      <c r="I5" s="63">
+        <v>3</v>
       </c>
       <c r="J5" s="7">
         <f t="shared" ref="J5:J12" si="0">G5/D60</f>
-        <v>0.37134328358208957</v>
+        <v>0.96955223880597019</v>
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="19" t="s">
@@ -1286,31 +1284,31 @@
       <c r="B6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="53">
-        <v>-32</v>
-      </c>
-      <c r="D6" s="53">
-        <v>-64</v>
-      </c>
-      <c r="E6" s="53">
-        <v>-32</v>
+      <c r="C6" s="52">
+        <v>-141</v>
+      </c>
+      <c r="D6" s="52">
+        <v>-128</v>
+      </c>
+      <c r="E6" s="63">
+        <v>13</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" ref="F6:F11" si="1">C6/C61</f>
-        <v>-4.784688995215311E-2</v>
-      </c>
-      <c r="G6" s="53">
-        <v>-128</v>
-      </c>
-      <c r="H6" s="53">
-        <v>-134</v>
-      </c>
-      <c r="I6" s="53">
-        <v>-6</v>
-      </c>
-      <c r="J6" s="10">
+        <v>-0.21082535885167467</v>
+      </c>
+      <c r="G6" s="63">
+        <v>470</v>
+      </c>
+      <c r="H6" s="63">
+        <v>469</v>
+      </c>
+      <c r="I6" s="52">
+        <v>-1</v>
+      </c>
+      <c r="J6" s="7">
         <f t="shared" si="0"/>
-        <v>-0.16842105263157894</v>
+        <v>0.61842105263157898</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="19" t="s">
@@ -1334,31 +1332,31 @@
       <c r="B7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="53">
-        <v>-335</v>
-      </c>
-      <c r="D7" s="53">
-        <v>-267</v>
-      </c>
-      <c r="E7" s="54">
-        <v>68</v>
-      </c>
-      <c r="F7" s="10">
+      <c r="C7" s="63">
+        <v>781</v>
+      </c>
+      <c r="D7" s="63">
+        <v>998</v>
+      </c>
+      <c r="E7" s="63">
+        <v>217</v>
+      </c>
+      <c r="F7" s="7">
         <f t="shared" si="1"/>
-        <v>-0.20022712330404638</v>
-      </c>
-      <c r="G7" s="54">
-        <v>1056</v>
-      </c>
-      <c r="H7" s="54">
-        <v>1211</v>
-      </c>
-      <c r="I7" s="54">
-        <v>155</v>
+        <v>0.46679815910585143</v>
+      </c>
+      <c r="G7" s="63">
+        <v>1354</v>
+      </c>
+      <c r="H7" s="63">
+        <v>1467</v>
+      </c>
+      <c r="I7" s="63">
+        <v>113</v>
       </c>
       <c r="J7" s="7">
         <f t="shared" si="0"/>
-        <v>0.55542406311637083</v>
+        <v>0.71216305062458907</v>
       </c>
       <c r="K7" s="5"/>
       <c r="L7" s="18" t="s">
@@ -1384,31 +1382,31 @@
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="53">
-        <v>-391</v>
-      </c>
-      <c r="D8" s="53">
-        <v>-389</v>
-      </c>
-      <c r="E8" s="54">
-        <v>2</v>
+      <c r="C8" s="52">
+        <v>-380</v>
+      </c>
+      <c r="D8" s="52">
+        <v>-536</v>
+      </c>
+      <c r="E8" s="52">
+        <v>-156</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-0.28390938135347082</v>
-      </c>
-      <c r="G8" s="53">
-        <v>-634</v>
-      </c>
-      <c r="H8" s="53">
-        <v>-207</v>
-      </c>
-      <c r="I8" s="54">
-        <v>427</v>
+        <v>-0.27592216090618643</v>
+      </c>
+      <c r="G8" s="52">
+        <v>-72</v>
+      </c>
+      <c r="H8" s="52">
+        <v>-142</v>
+      </c>
+      <c r="I8" s="52">
+        <v>-70</v>
       </c>
       <c r="J8" s="10">
         <f t="shared" si="0"/>
-        <v>-0.40511182108626198</v>
+        <v>-4.6006389776357827E-2</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="19" t="s">
@@ -1434,31 +1432,31 @@
       <c r="B9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="53">
-        <v>-119</v>
-      </c>
-      <c r="D9" s="53">
-        <v>-196</v>
-      </c>
-      <c r="E9" s="53">
-        <v>-77</v>
-      </c>
-      <c r="F9" s="10">
+      <c r="C9" s="63">
+        <v>104</v>
+      </c>
+      <c r="D9" s="52">
+        <v>-23</v>
+      </c>
+      <c r="E9" s="52">
+        <v>-127</v>
+      </c>
+      <c r="F9" s="7">
         <f t="shared" si="1"/>
-        <v>-8.9406461307287757E-2</v>
-      </c>
-      <c r="G9" s="54">
-        <v>592</v>
-      </c>
-      <c r="H9" s="54">
-        <v>1071</v>
-      </c>
-      <c r="I9" s="54">
-        <v>479</v>
+        <v>7.8136739293764093E-2</v>
+      </c>
+      <c r="G9" s="63">
+        <v>1442</v>
+      </c>
+      <c r="H9" s="63">
+        <v>1422</v>
+      </c>
+      <c r="I9" s="52">
+        <v>-20</v>
       </c>
       <c r="J9" s="7">
         <f t="shared" si="0"/>
-        <v>0.39140495867768593</v>
+        <v>0.95338842975206617</v>
       </c>
       <c r="K9" s="5"/>
       <c r="L9" s="19" t="s">
@@ -1484,31 +1482,31 @@
       <c r="B10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="53">
-        <v>-703</v>
-      </c>
-      <c r="D10" s="53">
-        <v>-217</v>
-      </c>
-      <c r="E10" s="54">
-        <v>486</v>
-      </c>
-      <c r="F10" s="10">
+      <c r="C10" s="63">
+        <v>883</v>
+      </c>
+      <c r="D10" s="63">
+        <v>936</v>
+      </c>
+      <c r="E10" s="63">
+        <v>53</v>
+      </c>
+      <c r="F10" s="7">
         <f t="shared" si="1"/>
-        <v>-0.2958754208754209</v>
-      </c>
-      <c r="G10" s="54">
-        <v>1569</v>
-      </c>
-      <c r="H10" s="54">
-        <v>1732</v>
-      </c>
-      <c r="I10" s="54">
-        <v>163</v>
+        <v>0.37163299663299665</v>
+      </c>
+      <c r="G10" s="63">
+        <v>2288</v>
+      </c>
+      <c r="H10" s="63">
+        <v>2287</v>
+      </c>
+      <c r="I10" s="52">
+        <v>-1</v>
       </c>
       <c r="J10" s="7">
         <f t="shared" si="0"/>
-        <v>0.58111111111111113</v>
+        <v>0.84740740740740739</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="19" t="s">
@@ -1532,31 +1530,31 @@
       <c r="B11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="54">
-        <v>322</v>
-      </c>
-      <c r="D11" s="54">
-        <v>288</v>
-      </c>
-      <c r="E11" s="53">
-        <v>-34</v>
+      <c r="C11" s="63">
+        <v>356</v>
+      </c>
+      <c r="D11" s="63">
+        <v>426</v>
+      </c>
+      <c r="E11" s="63">
+        <v>70</v>
       </c>
       <c r="F11" s="7">
         <f t="shared" si="1"/>
-        <v>0.36960514233241504</v>
-      </c>
-      <c r="G11" s="54">
-        <v>628</v>
-      </c>
-      <c r="H11" s="54">
-        <v>772</v>
-      </c>
-      <c r="I11" s="54">
-        <v>144</v>
+        <v>0.40863177226813591</v>
+      </c>
+      <c r="G11" s="63">
+        <v>988</v>
+      </c>
+      <c r="H11" s="63">
+        <v>988</v>
+      </c>
+      <c r="I11" s="63">
+        <v>0</v>
       </c>
       <c r="J11" s="7">
         <f t="shared" si="0"/>
-        <v>0.63434343434343432</v>
+        <v>0.99797979797979797</v>
       </c>
       <c r="K11" s="5"/>
       <c r="L11" s="18" t="s">
@@ -1582,31 +1580,31 @@
       <c r="B12" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="55">
-        <v>-1769</v>
-      </c>
-      <c r="D12" s="55">
-        <v>-1908</v>
-      </c>
-      <c r="E12" s="55">
-        <v>-139</v>
-      </c>
-      <c r="F12" s="52">
+      <c r="C12" s="64">
+        <v>1680</v>
+      </c>
+      <c r="D12" s="64">
+        <v>1895</v>
+      </c>
+      <c r="E12" s="64">
+        <v>215</v>
+      </c>
+      <c r="F12" s="9">
         <f>C12/C67</f>
-        <v>-0.18132617185498007</v>
-      </c>
-      <c r="G12" s="56">
-        <v>3707</v>
-      </c>
-      <c r="H12" s="56">
-        <v>5184</v>
-      </c>
-      <c r="I12" s="56">
-        <v>1477</v>
+        <v>0.17193208682570385</v>
+      </c>
+      <c r="G12" s="64">
+        <v>8094</v>
+      </c>
+      <c r="H12" s="64">
+        <v>8118</v>
+      </c>
+      <c r="I12" s="64">
+        <v>24</v>
       </c>
       <c r="J12" s="9">
         <f t="shared" si="0"/>
-        <v>0.33437817115796598</v>
+        <v>0.72894292468760558</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="19" t="s">
@@ -1632,24 +1630,24 @@
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="65"/>
-      <c r="B13" s="61"/>
-      <c r="C13" s="66" t="s">
+      <c r="A13" s="61"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="61"/>
-      <c r="E13" s="66">
+      <c r="D13" s="57"/>
+      <c r="E13" s="62">
         <v>22</v>
       </c>
-      <c r="F13" s="61"/>
-      <c r="G13" s="66" t="s">
+      <c r="F13" s="57"/>
+      <c r="G13" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="61"/>
-      <c r="I13" s="66">
+      <c r="H13" s="57"/>
+      <c r="I13" s="62">
         <v>25</v>
       </c>
-      <c r="J13" s="61"/>
+      <c r="J13" s="57"/>
       <c r="K13" s="5"/>
       <c r="L13" s="19" t="s">
         <v>19</v>
@@ -3320,15 +3318,15 @@
         <v>98</v>
       </c>
       <c r="B67" s="5">
-        <v>8869</v>
+        <v>8883</v>
       </c>
       <c r="C67" s="5">
         <f t="shared" si="3"/>
-        <v>9755.9</v>
+        <v>9771.2999999999993</v>
       </c>
       <c r="D67" s="5">
         <f t="shared" si="2"/>
-        <v>11086.25</v>
+        <v>11103.75</v>
       </c>
       <c r="L67" s="27"/>
       <c r="M67" s="27"/>

--- a/template.xlsx
+++ b/template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\1. Work\1. Daily\Capacity Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08585676-006E-4F97-9BE7-218C847D9F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686AACC4-307D-459E-A2CD-42A595D57FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="810" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -396,10 +396,10 @@
     <t>Available Capacity (First)</t>
   </si>
   <si>
-    <t>May</t>
-  </si>
-  <si>
-    <t>June</t>
+    <t>July</t>
+  </si>
+  <si>
+    <t>August</t>
   </si>
 </sst>
 </file>
@@ -409,7 +409,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -452,13 +452,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -490,6 +483,18 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -688,7 +693,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -698,47 +703,45 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="12" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="12" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="11" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="11" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="11" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -757,7 +760,12 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1101,18 +1109,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
+      <c r="A1" s="56" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
       <c r="K1" s="5"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1129,103 +1137,103 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="5"/>
-      <c r="L2" s="16" t="s">
+      <c r="L2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="17"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C3" s="58" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="58" t="s">
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="61" t="s">
         <v>119</v>
       </c>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="57"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="60"/>
       <c r="K3" s="5"/>
-      <c r="L3" s="18" t="s">
+      <c r="L3" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="18" t="s">
+      <c r="M3" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="18" t="s">
+      <c r="N3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="O3" s="18" t="s">
+      <c r="O3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="18" t="s">
+      <c r="P3" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="Q3" s="18" t="s">
+      <c r="Q3" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="R3" s="18" t="s">
+      <c r="R3" s="16" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="60"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="50">
+      <c r="A4" s="63"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="48">
         <f ca="1">TODAY()</f>
-        <v>46117</v>
-      </c>
-      <c r="D4" s="50">
+        <v>46204</v>
+      </c>
+      <c r="D4" s="48">
         <f ca="1">C4-1</f>
-        <v>46116</v>
-      </c>
-      <c r="E4" s="51" t="s">
+        <v>46203</v>
+      </c>
+      <c r="E4" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="51" t="s">
+      <c r="F4" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="50">
-        <f ca="1">TODAY()</f>
-        <v>46117</v>
-      </c>
-      <c r="H4" s="50">
-        <f ca="1">G4-1</f>
-        <v>46116</v>
-      </c>
-      <c r="I4" s="51" t="s">
+      <c r="G4" s="48">
+        <f ca="1">C4</f>
+        <v>46204</v>
+      </c>
+      <c r="H4" s="48">
+        <f ca="1">D4</f>
+        <v>46203</v>
+      </c>
+      <c r="I4" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="J4" s="51" t="s">
+      <c r="J4" s="49" t="s">
         <v>13</v>
       </c>
       <c r="K4" s="5"/>
-      <c r="L4" s="19" t="s">
+      <c r="L4" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="M4" s="19" t="s">
+      <c r="M4" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="N4" s="20">
+      <c r="N4" s="18">
         <v>135334</v>
       </c>
-      <c r="O4" s="20"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -1234,48 +1242,48 @@
       <c r="B5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="63">
-        <v>77</v>
-      </c>
-      <c r="D5" s="63">
-        <v>221</v>
-      </c>
-      <c r="E5" s="63">
-        <v>144</v>
-      </c>
-      <c r="F5" s="7">
+      <c r="C5" s="53">
+        <v>-586</v>
+      </c>
+      <c r="D5" s="53">
+        <v>-539</v>
+      </c>
+      <c r="E5" s="53">
+        <v>47</v>
+      </c>
+      <c r="F5" s="51">
         <f>C5/C60</f>
-        <v>5.2238805970149252E-2</v>
-      </c>
-      <c r="G5" s="63">
-        <v>1624</v>
-      </c>
-      <c r="H5" s="63">
-        <v>1627</v>
-      </c>
-      <c r="I5" s="63">
-        <v>3</v>
+        <v>-0.33639494833524686</v>
+      </c>
+      <c r="G5" s="66">
+        <v>1214</v>
+      </c>
+      <c r="H5" s="66">
+        <v>1378</v>
+      </c>
+      <c r="I5" s="66">
+        <v>164</v>
       </c>
       <c r="J5" s="7">
-        <f t="shared" ref="J5:J12" si="0">G5/D60</f>
-        <v>0.96955223880597019</v>
+        <f>G5/D60</f>
+        <v>0.72477611940298503</v>
       </c>
       <c r="K5" s="5"/>
-      <c r="L5" s="19" t="s">
+      <c r="L5" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="M5" s="19" t="s">
+      <c r="M5" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="N5" s="20">
+      <c r="N5" s="18">
         <v>659019</v>
       </c>
-      <c r="O5" s="20">
+      <c r="O5" s="18">
         <v>28758</v>
       </c>
-      <c r="P5" s="20"/>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="19"/>
+      <c r="P5" s="18"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
@@ -1284,46 +1292,46 @@
       <c r="B6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="52">
-        <v>-141</v>
-      </c>
-      <c r="D6" s="52">
-        <v>-128</v>
-      </c>
-      <c r="E6" s="63">
-        <v>13</v>
-      </c>
-      <c r="F6" s="10">
-        <f t="shared" ref="F6:F11" si="1">C6/C61</f>
-        <v>-0.21082535885167467</v>
-      </c>
-      <c r="G6" s="63">
-        <v>470</v>
-      </c>
-      <c r="H6" s="63">
-        <v>469</v>
-      </c>
-      <c r="I6" s="52">
-        <v>-1</v>
+      <c r="C6" s="53">
+        <v>-227</v>
+      </c>
+      <c r="D6" s="53">
+        <v>-105</v>
+      </c>
+      <c r="E6" s="54">
+        <v>122</v>
+      </c>
+      <c r="F6" s="51">
+        <f t="shared" ref="F6:F11" si="0">C6/C61</f>
+        <v>-0.28719635627530365</v>
+      </c>
+      <c r="G6" s="66">
+        <v>199</v>
+      </c>
+      <c r="H6" s="66">
+        <v>278</v>
+      </c>
+      <c r="I6" s="66">
+        <v>79</v>
       </c>
       <c r="J6" s="7">
-        <f t="shared" si="0"/>
-        <v>0.61842105263157898</v>
+        <f t="shared" ref="J6:J12" si="1">G6/D61</f>
+        <v>0.26184210526315788</v>
       </c>
       <c r="K6" s="5"/>
-      <c r="L6" s="19" t="s">
+      <c r="L6" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="M6" s="19" t="s">
+      <c r="M6" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="N6" s="20">
+      <c r="N6" s="18">
         <v>2500</v>
       </c>
-      <c r="O6" s="20"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19"/>
-      <c r="R6" s="19"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
@@ -1332,48 +1340,48 @@
       <c r="B7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="63">
-        <v>781</v>
-      </c>
-      <c r="D7" s="63">
-        <v>998</v>
-      </c>
-      <c r="E7" s="63">
-        <v>217</v>
-      </c>
-      <c r="F7" s="7">
+      <c r="C7" s="53">
+        <v>-140</v>
+      </c>
+      <c r="D7" s="53">
+        <v>-40</v>
+      </c>
+      <c r="E7" s="53">
+        <v>100</v>
+      </c>
+      <c r="F7" s="51">
+        <f t="shared" si="0"/>
+        <v>-7.0803621099479089E-2</v>
+      </c>
+      <c r="G7" s="66">
+        <v>1132</v>
+      </c>
+      <c r="H7" s="66">
+        <v>1287</v>
+      </c>
+      <c r="I7" s="66">
+        <v>155</v>
+      </c>
+      <c r="J7" s="7">
         <f t="shared" si="1"/>
-        <v>0.46679815910585143</v>
-      </c>
-      <c r="G7" s="63">
-        <v>1354</v>
-      </c>
-      <c r="H7" s="63">
-        <v>1467</v>
-      </c>
-      <c r="I7" s="63">
-        <v>113</v>
-      </c>
-      <c r="J7" s="7">
-        <f t="shared" si="0"/>
-        <v>0.71216305062458907</v>
+        <v>0.59539776462853389</v>
       </c>
       <c r="K7" s="5"/>
-      <c r="L7" s="18" t="s">
+      <c r="L7" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="M7" s="18" t="s">
+      <c r="M7" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="N7" s="22">
+      <c r="N7" s="20">
         <v>796854</v>
       </c>
-      <c r="O7" s="22">
+      <c r="O7" s="20">
         <v>28758</v>
       </c>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="18"/>
-      <c r="R7" s="18"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="16"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -1382,48 +1390,48 @@
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="52">
-        <v>-380</v>
-      </c>
-      <c r="D8" s="52">
-        <v>-536</v>
-      </c>
-      <c r="E8" s="52">
-        <v>-156</v>
-      </c>
-      <c r="F8" s="10">
+      <c r="C8" s="54">
+        <v>-33</v>
+      </c>
+      <c r="D8" s="53">
+        <v>1</v>
+      </c>
+      <c r="E8" s="53">
+        <v>34</v>
+      </c>
+      <c r="F8" s="51">
+        <f t="shared" si="0"/>
+        <v>-2.0275251904644874E-2</v>
+      </c>
+      <c r="G8" s="24">
+        <v>-149</v>
+      </c>
+      <c r="H8" s="24">
+        <v>-12</v>
+      </c>
+      <c r="I8" s="66">
+        <v>137</v>
+      </c>
+      <c r="J8" s="51">
         <f t="shared" si="1"/>
-        <v>-0.27592216090618643</v>
-      </c>
-      <c r="G8" s="52">
-        <v>-72</v>
-      </c>
-      <c r="H8" s="52">
-        <v>-142</v>
-      </c>
-      <c r="I8" s="52">
-        <v>-70</v>
-      </c>
-      <c r="J8" s="10">
-        <f t="shared" si="0"/>
-        <v>-4.6006389776357827E-2</v>
+        <v>-9.5207667731629392E-2</v>
       </c>
       <c r="K8" s="5"/>
-      <c r="L8" s="19" t="s">
+      <c r="L8" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="M8" s="19" t="s">
+      <c r="M8" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N8" s="20">
+      <c r="N8" s="18">
         <v>140567</v>
       </c>
-      <c r="O8" s="20">
+      <c r="O8" s="18">
         <v>7595</v>
       </c>
-      <c r="P8" s="20"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="19"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
@@ -1432,48 +1440,48 @@
       <c r="B9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="63">
-        <v>104</v>
-      </c>
-      <c r="D9" s="52">
-        <v>-23</v>
-      </c>
-      <c r="E9" s="52">
-        <v>-127</v>
-      </c>
-      <c r="F9" s="7">
+      <c r="C9" s="53">
+        <v>-228</v>
+      </c>
+      <c r="D9" s="53">
+        <v>-305</v>
+      </c>
+      <c r="E9" s="54">
+        <v>-77</v>
+      </c>
+      <c r="F9" s="51">
+        <f t="shared" si="0"/>
+        <v>-0.1449459631277813</v>
+      </c>
+      <c r="G9" s="66">
+        <v>920</v>
+      </c>
+      <c r="H9" s="66">
+        <v>984</v>
+      </c>
+      <c r="I9" s="66">
+        <v>64</v>
+      </c>
+      <c r="J9" s="7">
         <f t="shared" si="1"/>
-        <v>7.8136739293764093E-2</v>
-      </c>
-      <c r="G9" s="63">
-        <v>1442</v>
-      </c>
-      <c r="H9" s="63">
-        <v>1422</v>
-      </c>
-      <c r="I9" s="52">
-        <v>-20</v>
-      </c>
-      <c r="J9" s="7">
-        <f t="shared" si="0"/>
-        <v>0.95338842975206617</v>
+        <v>0.60826446280991731</v>
       </c>
       <c r="K9" s="5"/>
-      <c r="L9" s="19" t="s">
+      <c r="L9" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="M9" s="19" t="s">
+      <c r="M9" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="N9" s="20">
+      <c r="N9" s="18">
         <v>462779</v>
       </c>
-      <c r="O9" s="20">
+      <c r="O9" s="18">
         <v>2396</v>
       </c>
-      <c r="P9" s="20"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="19"/>
+      <c r="P9" s="18"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
@@ -1482,46 +1490,46 @@
       <c r="B10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="63">
-        <v>883</v>
-      </c>
-      <c r="D10" s="63">
-        <v>936</v>
-      </c>
-      <c r="E10" s="63">
-        <v>53</v>
-      </c>
-      <c r="F10" s="7">
+      <c r="C10" s="53">
+        <v>-1001</v>
+      </c>
+      <c r="D10" s="53">
+        <v>-425</v>
+      </c>
+      <c r="E10" s="54">
+        <v>576</v>
+      </c>
+      <c r="F10" s="51">
+        <f t="shared" si="0"/>
+        <v>-0.35648148148148145</v>
+      </c>
+      <c r="G10" s="66">
+        <v>2058</v>
+      </c>
+      <c r="H10" s="66">
+        <v>2261</v>
+      </c>
+      <c r="I10" s="66">
+        <v>203</v>
+      </c>
+      <c r="J10" s="7">
         <f t="shared" si="1"/>
-        <v>0.37163299663299665</v>
-      </c>
-      <c r="G10" s="63">
-        <v>2288</v>
-      </c>
-      <c r="H10" s="63">
-        <v>2287</v>
-      </c>
-      <c r="I10" s="52">
-        <v>-1</v>
-      </c>
-      <c r="J10" s="7">
-        <f t="shared" si="0"/>
-        <v>0.84740740740740739</v>
+        <v>0.76222222222222225</v>
       </c>
       <c r="K10" s="5"/>
-      <c r="L10" s="19" t="s">
+      <c r="L10" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="M10" s="19" t="s">
+      <c r="M10" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="N10" s="20">
+      <c r="N10" s="18">
         <v>9112</v>
       </c>
-      <c r="O10" s="19"/>
-      <c r="P10" s="19"/>
-      <c r="Q10" s="19"/>
-      <c r="R10" s="19"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
@@ -1530,48 +1538,48 @@
       <c r="B11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="63">
-        <v>356</v>
-      </c>
-      <c r="D11" s="63">
-        <v>426</v>
-      </c>
-      <c r="E11" s="63">
-        <v>70</v>
-      </c>
-      <c r="F11" s="7">
+      <c r="C11" s="53">
+        <v>-112</v>
+      </c>
+      <c r="D11" s="53">
+        <v>-82</v>
+      </c>
+      <c r="E11" s="53">
+        <v>30</v>
+      </c>
+      <c r="F11" s="51">
+        <f t="shared" si="0"/>
+        <v>-0.10878010878010877</v>
+      </c>
+      <c r="G11" s="66">
+        <v>674</v>
+      </c>
+      <c r="H11" s="66">
+        <v>624</v>
+      </c>
+      <c r="I11" s="24">
+        <v>-50</v>
+      </c>
+      <c r="J11" s="7">
         <f t="shared" si="1"/>
-        <v>0.40863177226813591</v>
-      </c>
-      <c r="G11" s="63">
-        <v>988</v>
-      </c>
-      <c r="H11" s="63">
-        <v>988</v>
-      </c>
-      <c r="I11" s="63">
-        <v>0</v>
-      </c>
-      <c r="J11" s="7">
-        <f t="shared" si="0"/>
-        <v>0.99797979797979797</v>
+        <v>0.68080808080808086</v>
       </c>
       <c r="K11" s="5"/>
-      <c r="L11" s="18" t="s">
+      <c r="L11" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="M11" s="18" t="s">
+      <c r="M11" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="N11" s="22">
+      <c r="N11" s="20">
         <v>612459</v>
       </c>
-      <c r="O11" s="22">
+      <c r="O11" s="20">
         <v>9991</v>
       </c>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="18"/>
-      <c r="R11" s="18"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="16"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
@@ -1580,94 +1588,94 @@
       <c r="B12" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="64">
-        <v>1680</v>
-      </c>
-      <c r="D12" s="64">
-        <v>1895</v>
-      </c>
-      <c r="E12" s="64">
-        <v>215</v>
-      </c>
-      <c r="F12" s="9">
+      <c r="C12" s="55">
+        <v>-2328</v>
+      </c>
+      <c r="D12" s="55">
+        <v>-1494</v>
+      </c>
+      <c r="E12" s="55">
+        <v>834</v>
+      </c>
+      <c r="F12" s="52">
         <f>C12/C67</f>
-        <v>0.17193208682570385</v>
-      </c>
-      <c r="G12" s="64">
-        <v>8094</v>
-      </c>
-      <c r="H12" s="64">
-        <v>8118</v>
-      </c>
-      <c r="I12" s="64">
-        <v>24</v>
-      </c>
-      <c r="J12" s="9">
-        <f t="shared" si="0"/>
-        <v>0.72894292468760558</v>
+        <v>-0.20159509521211649</v>
+      </c>
+      <c r="G12" s="67">
+        <v>6049</v>
+      </c>
+      <c r="H12" s="67">
+        <v>6800</v>
+      </c>
+      <c r="I12" s="67">
+        <v>751</v>
+      </c>
+      <c r="J12" s="50">
+        <f t="shared" si="1"/>
+        <v>0.54477091072835748</v>
       </c>
       <c r="K12" s="5"/>
-      <c r="L12" s="19" t="s">
+      <c r="L12" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="M12" s="19" t="s">
+      <c r="M12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="N12" s="20">
+      <c r="N12" s="18">
         <v>977135</v>
       </c>
-      <c r="O12" s="19">
+      <c r="O12" s="17">
         <v>340985</v>
       </c>
-      <c r="P12" s="19">
+      <c r="P12" s="17">
         <v>421696</v>
       </c>
-      <c r="Q12" s="19">
+      <c r="Q12" s="17">
         <v>199787</v>
       </c>
-      <c r="R12" s="19">
+      <c r="R12" s="17">
         <v>1993</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="61"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="62" t="s">
+      <c r="A13" s="64"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="57"/>
-      <c r="E13" s="62">
-        <v>22</v>
-      </c>
-      <c r="F13" s="57"/>
-      <c r="G13" s="62" t="s">
+      <c r="D13" s="60"/>
+      <c r="E13" s="65">
+        <v>26</v>
+      </c>
+      <c r="F13" s="60"/>
+      <c r="G13" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="57"/>
-      <c r="I13" s="62">
+      <c r="H13" s="60"/>
+      <c r="I13" s="65">
         <v>25</v>
       </c>
-      <c r="J13" s="57"/>
+      <c r="J13" s="60"/>
       <c r="K13" s="5"/>
-      <c r="L13" s="19" t="s">
+      <c r="L13" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="M13" s="19" t="s">
+      <c r="M13" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="N13" s="20">
+      <c r="N13" s="18">
         <v>115236</v>
       </c>
-      <c r="O13" s="20">
+      <c r="O13" s="18">
         <v>60962</v>
       </c>
-      <c r="P13" s="20">
+      <c r="P13" s="18">
         <v>1608</v>
       </c>
-      <c r="Q13" s="20">
+      <c r="Q13" s="18">
         <v>13212</v>
       </c>
-      <c r="R13" s="20"/>
+      <c r="R13" s="18"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
@@ -1681,28 +1689,28 @@
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
-      <c r="L14" s="19" t="s">
+      <c r="L14" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="M14" s="19" t="s">
+      <c r="M14" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="N14" s="20">
+      <c r="N14" s="18">
         <v>55588</v>
       </c>
-      <c r="O14" s="20">
+      <c r="O14" s="18">
         <v>7350</v>
       </c>
-      <c r="P14" s="20"/>
-      <c r="Q14" s="19"/>
-      <c r="R14" s="20"/>
+      <c r="P14" s="18"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="18"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="21" t="s">
         <v>32</v>
       </c>
       <c r="B15" s="3"/>
-      <c r="C15" s="24">
+      <c r="C15" s="22">
         <v>14378307</v>
       </c>
       <c r="D15" s="5"/>
@@ -1713,25 +1721,25 @@
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
-      <c r="L15" s="18" t="s">
+      <c r="L15" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="M15" s="18" t="s">
+      <c r="M15" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="N15" s="22">
+      <c r="N15" s="20">
         <v>1147959</v>
       </c>
-      <c r="O15" s="22">
+      <c r="O15" s="20">
         <v>409297</v>
       </c>
-      <c r="P15" s="22">
+      <c r="P15" s="20">
         <v>423304</v>
       </c>
-      <c r="Q15" s="22">
+      <c r="Q15" s="20">
         <v>212999</v>
       </c>
-      <c r="R15" s="22">
+      <c r="R15" s="20">
         <v>1993</v>
       </c>
     </row>
@@ -1747,1410 +1755,1410 @@
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
-      <c r="L16" s="19" t="s">
+      <c r="L16" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="M16" s="19" t="s">
+      <c r="M16" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="N16" s="20">
+      <c r="N16" s="18">
         <v>407703</v>
       </c>
-      <c r="O16" s="19">
+      <c r="O16" s="17">
         <v>2302</v>
       </c>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="19"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="17"/>
     </row>
     <row r="17" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
       <c r="K17" s="5"/>
-      <c r="L17" s="19" t="s">
+      <c r="L17" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="M17" s="19" t="s">
+      <c r="M17" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="N17" s="20">
+      <c r="N17" s="18">
         <v>30207</v>
       </c>
-      <c r="O17" s="19">
+      <c r="O17" s="17">
         <v>307</v>
       </c>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="19"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="17"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="I18" s="12" t="s">
+      <c r="I18" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="J18" s="12" t="s">
+      <c r="J18" s="10" t="s">
         <v>43</v>
       </c>
       <c r="K18" s="5"/>
-      <c r="L18" s="19" t="s">
+      <c r="L18" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="M18" s="19" t="s">
+      <c r="M18" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="N18" s="20">
+      <c r="N18" s="18">
         <v>2285</v>
       </c>
-      <c r="O18" s="20">
+      <c r="O18" s="18">
         <v>11379</v>
       </c>
-      <c r="P18" s="20"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="19"/>
+      <c r="P18" s="18"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="17"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="21">
+      <c r="C19" s="19">
         <v>-77</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="12">
         <v>84</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="12">
         <v>226</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="12">
         <v>278</v>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="12">
         <v>366</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="12">
         <v>388</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="12">
         <v>401</v>
       </c>
-      <c r="J19" s="14">
+      <c r="J19" s="12">
         <v>201</v>
       </c>
       <c r="K19" s="5"/>
-      <c r="L19" s="19" t="s">
+      <c r="L19" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="M19" s="19" t="s">
+      <c r="M19" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="N19" s="20">
+      <c r="N19" s="18">
         <v>10720</v>
       </c>
-      <c r="O19" s="20"/>
-      <c r="P19" s="20"/>
-      <c r="Q19" s="19"/>
-      <c r="R19" s="19"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="21">
+      <c r="C20" s="19">
         <v>-31</v>
       </c>
-      <c r="D20" s="21">
+      <c r="D20" s="19">
         <v>-54</v>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="19">
         <v>-25</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="12">
         <v>2</v>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="12">
         <v>87</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="12">
         <v>166</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="12">
         <v>148</v>
       </c>
-      <c r="J20" s="14">
+      <c r="J20" s="12">
         <v>66</v>
       </c>
       <c r="K20" s="5"/>
-      <c r="L20" s="19" t="s">
+      <c r="L20" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="M20" s="19" t="s">
+      <c r="M20" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="N20" s="20">
+      <c r="N20" s="18">
         <v>48884</v>
       </c>
-      <c r="O20" s="20"/>
-      <c r="P20" s="20"/>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="19"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="18"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="19">
         <v>-59</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="12">
         <v>57</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="12">
         <v>70</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="12">
         <v>149</v>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="12">
         <v>272</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="12">
         <v>341</v>
       </c>
-      <c r="I21" s="14">
+      <c r="I21" s="12">
         <v>350</v>
       </c>
-      <c r="J21" s="14">
+      <c r="J21" s="12">
         <v>181</v>
       </c>
       <c r="K21" s="5"/>
-      <c r="L21" s="19" t="s">
+      <c r="L21" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="M21" s="19" t="s">
+      <c r="M21" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="N21" s="20">
+      <c r="N21" s="18">
         <v>84417</v>
       </c>
-      <c r="O21" s="20"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="19"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="17"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="12">
         <v>20</v>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="19">
         <v>-70</v>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="19">
         <v>-84</v>
       </c>
-      <c r="F22" s="21">
+      <c r="F22" s="19">
         <v>-100</v>
       </c>
-      <c r="G22" s="21">
+      <c r="G22" s="19">
         <v>-146</v>
       </c>
-      <c r="H22" s="21">
+      <c r="H22" s="19">
         <v>-186</v>
       </c>
-      <c r="I22" s="21">
+      <c r="I22" s="19">
         <v>-146</v>
       </c>
-      <c r="J22" s="21">
+      <c r="J22" s="19">
         <v>-53</v>
       </c>
       <c r="K22" s="5"/>
-      <c r="L22" s="19" t="s">
+      <c r="L22" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="M22" s="19" t="s">
+      <c r="M22" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="N22" s="20">
+      <c r="N22" s="18">
         <v>14714</v>
       </c>
-      <c r="O22" s="20"/>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
-      <c r="R22" s="19"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="17"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="21">
+      <c r="C23" s="19">
         <v>-85</v>
       </c>
-      <c r="D23" s="21">
+      <c r="D23" s="19">
         <v>-36</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E23" s="12">
         <v>168</v>
       </c>
-      <c r="F23" s="14">
+      <c r="F23" s="12">
         <v>305</v>
       </c>
-      <c r="G23" s="14">
+      <c r="G23" s="12">
         <v>382</v>
       </c>
-      <c r="H23" s="14">
+      <c r="H23" s="12">
         <v>377</v>
       </c>
-      <c r="I23" s="14">
+      <c r="I23" s="12">
         <v>387</v>
       </c>
-      <c r="J23" s="14">
+      <c r="J23" s="12">
         <v>193</v>
       </c>
       <c r="K23" s="5"/>
-      <c r="L23" s="19" t="s">
+      <c r="L23" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="M23" s="19" t="s">
+      <c r="M23" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="N23" s="20">
+      <c r="N23" s="18">
         <v>53962</v>
       </c>
-      <c r="O23" s="20">
+      <c r="O23" s="18">
         <v>7943</v>
       </c>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
-      <c r="R23" s="19"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="17"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="21">
+      <c r="C24" s="19">
         <v>-32</v>
       </c>
-      <c r="D24" s="21">
+      <c r="D24" s="19">
         <v>-13</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="12">
         <v>67</v>
       </c>
-      <c r="F24" s="14">
+      <c r="F24" s="12">
         <v>196</v>
       </c>
-      <c r="G24" s="14">
+      <c r="G24" s="12">
         <v>401</v>
       </c>
-      <c r="H24" s="14">
+      <c r="H24" s="12">
         <v>451</v>
       </c>
-      <c r="I24" s="14">
+      <c r="I24" s="12">
         <v>497</v>
       </c>
-      <c r="J24" s="14">
+      <c r="J24" s="12">
         <v>229</v>
       </c>
       <c r="K24" s="5"/>
-      <c r="L24" s="19" t="s">
+      <c r="L24" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="N24" s="20">
+      <c r="N24" s="18">
         <v>168263</v>
       </c>
-      <c r="O24" s="20">
+      <c r="O24" s="18">
         <v>147858</v>
       </c>
-      <c r="P24" s="20">
+      <c r="P24" s="18">
         <v>3071</v>
       </c>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="19"/>
+      <c r="Q24" s="17"/>
+      <c r="R24" s="17"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="12">
         <v>238</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="12">
         <v>198</v>
       </c>
-      <c r="E25" s="14">
+      <c r="E25" s="12">
         <v>198</v>
       </c>
-      <c r="F25" s="14">
+      <c r="F25" s="12">
         <v>198</v>
       </c>
-      <c r="G25" s="14">
+      <c r="G25" s="12">
         <v>238</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H25" s="12">
         <v>238</v>
       </c>
-      <c r="I25" s="14">
+      <c r="I25" s="12">
         <v>238</v>
       </c>
-      <c r="J25" s="14">
+      <c r="J25" s="12">
         <v>119</v>
       </c>
       <c r="K25" s="5"/>
-      <c r="L25" s="19" t="s">
+      <c r="L25" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="M25" s="19" t="s">
+      <c r="M25" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="N25" s="20">
+      <c r="N25" s="18">
         <v>96589</v>
       </c>
-      <c r="O25" s="20">
+      <c r="O25" s="18">
         <v>24323</v>
       </c>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="20">
+      <c r="P25" s="17"/>
+      <c r="Q25" s="18">
         <v>2002</v>
       </c>
-      <c r="R25" s="19"/>
+      <c r="R25" s="17"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="23">
         <v>-27</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="13">
         <v>165</v>
       </c>
-      <c r="E26" s="15">
+      <c r="E26" s="13">
         <v>621</v>
       </c>
-      <c r="F26" s="15">
+      <c r="F26" s="13">
         <v>1029</v>
       </c>
-      <c r="G26" s="15">
+      <c r="G26" s="13">
         <v>1599</v>
       </c>
-      <c r="H26" s="15">
+      <c r="H26" s="13">
         <v>1775</v>
       </c>
-      <c r="I26" s="15">
+      <c r="I26" s="13">
         <v>1875</v>
       </c>
-      <c r="J26" s="15">
+      <c r="J26" s="13">
         <v>935</v>
       </c>
       <c r="K26" s="5"/>
-      <c r="L26" s="19" t="s">
+      <c r="L26" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="M26" s="19" t="s">
+      <c r="M26" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="N26" s="20">
+      <c r="N26" s="18">
         <v>4472</v>
       </c>
-      <c r="O26" s="20">
+      <c r="O26" s="18">
         <v>15969</v>
       </c>
-      <c r="P26" s="20"/>
-      <c r="Q26" s="20"/>
-      <c r="R26" s="19"/>
+      <c r="P26" s="18"/>
+      <c r="Q26" s="18"/>
+      <c r="R26" s="17"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="L27" s="19" t="s">
+      <c r="L27" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="M27" s="19" t="s">
+      <c r="M27" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="N27" s="20">
+      <c r="N27" s="18">
         <v>4295</v>
       </c>
-      <c r="O27" s="20">
+      <c r="O27" s="18">
         <v>14703</v>
       </c>
-      <c r="P27" s="20"/>
-      <c r="Q27" s="20"/>
-      <c r="R27" s="19"/>
+      <c r="P27" s="18"/>
+      <c r="Q27" s="18"/>
+      <c r="R27" s="17"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="L28" s="18" t="s">
+      <c r="L28" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="M28" s="18" t="s">
+      <c r="M28" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="N28" s="22">
+      <c r="N28" s="20">
         <v>926510</v>
       </c>
-      <c r="O28" s="22">
+      <c r="O28" s="20">
         <v>224784</v>
       </c>
-      <c r="P28" s="22">
+      <c r="P28" s="20">
         <v>3071</v>
       </c>
-      <c r="Q28" s="22">
+      <c r="Q28" s="20">
         <v>2002</v>
       </c>
-      <c r="R28" s="18"/>
+      <c r="R28" s="16"/>
     </row>
     <row r="29" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="40" t="s">
+      <c r="B29" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="41"/>
-      <c r="L29" s="19" t="s">
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="39"/>
+      <c r="L29" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="M29" s="19" t="s">
+      <c r="M29" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="N29" s="20">
+      <c r="N29" s="18">
         <v>328272</v>
       </c>
-      <c r="O29" s="20">
+      <c r="O29" s="18">
         <v>46710</v>
       </c>
-      <c r="P29" s="20">
+      <c r="P29" s="18">
         <v>14980</v>
       </c>
-      <c r="Q29" s="19"/>
-      <c r="R29" s="19"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="17"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B30" s="42" t="s">
+      <c r="B30" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="C30" s="42" t="s">
+      <c r="C30" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="D30" s="42" t="s">
+      <c r="D30" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="E30" s="42" t="s">
+      <c r="E30" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F30" s="42" t="s">
+      <c r="F30" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="G30" s="42" t="s">
+      <c r="G30" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="H30" s="42" t="s">
+      <c r="H30" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="L30" s="19" t="s">
+      <c r="L30" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="M30" s="19" t="s">
+      <c r="M30" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="N30" s="20">
+      <c r="N30" s="18">
         <v>33234</v>
       </c>
-      <c r="O30" s="19">
+      <c r="O30" s="17">
         <v>15041</v>
       </c>
-      <c r="P30" s="19"/>
-      <c r="Q30" s="19"/>
-      <c r="R30" s="19"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17"/>
+      <c r="R30" s="17"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B31" s="43" t="s">
+      <c r="B31" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="44">
+      <c r="C31" s="42">
         <v>2039358</v>
       </c>
-      <c r="D31" s="44">
+      <c r="D31" s="42">
         <v>2049066</v>
       </c>
-      <c r="E31" s="26">
+      <c r="E31" s="24">
         <v>-9708</v>
       </c>
-      <c r="F31" s="44">
+      <c r="F31" s="42">
         <v>485782</v>
       </c>
-      <c r="G31" s="44">
+      <c r="G31" s="42">
         <v>485394</v>
       </c>
-      <c r="H31" s="44">
+      <c r="H31" s="42">
         <v>388</v>
       </c>
-      <c r="L31" s="19" t="s">
+      <c r="L31" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="M31" s="19" t="s">
+      <c r="M31" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="N31" s="20">
+      <c r="N31" s="18">
         <v>309529</v>
       </c>
-      <c r="O31" s="19">
+      <c r="O31" s="17">
         <v>15518</v>
       </c>
-      <c r="P31" s="19"/>
-      <c r="Q31" s="19"/>
-      <c r="R31" s="19"/>
+      <c r="P31" s="17"/>
+      <c r="Q31" s="17"/>
+      <c r="R31" s="17"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B32" s="43" t="s">
+      <c r="B32" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="C32" s="44">
+      <c r="C32" s="42">
         <v>148470</v>
       </c>
-      <c r="D32" s="44">
+      <c r="D32" s="42">
         <v>121000</v>
       </c>
-      <c r="E32" s="44">
+      <c r="E32" s="42">
         <v>27470</v>
       </c>
-      <c r="F32" s="44">
+      <c r="F32" s="42">
         <v>76003</v>
       </c>
-      <c r="G32" s="44">
+      <c r="G32" s="42">
         <v>60962</v>
       </c>
-      <c r="H32" s="44">
+      <c r="H32" s="42">
         <v>15041</v>
       </c>
-      <c r="L32" s="19" t="s">
+      <c r="L32" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="M32" s="19" t="s">
+      <c r="M32" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="N32" s="20">
+      <c r="N32" s="18">
         <v>391334</v>
       </c>
-      <c r="O32" s="19">
+      <c r="O32" s="17">
         <v>44302</v>
       </c>
-      <c r="P32" s="19"/>
-      <c r="Q32" s="19"/>
-      <c r="R32" s="19"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17"/>
+      <c r="R32" s="17"/>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B33" s="43" t="s">
+      <c r="B33" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="C33" s="44">
+      <c r="C33" s="42">
         <v>30207</v>
       </c>
-      <c r="D33" s="44">
+      <c r="D33" s="42">
         <v>30207</v>
       </c>
-      <c r="E33" s="44">
-        <v>0</v>
-      </c>
-      <c r="F33" s="44">
+      <c r="E33" s="42">
+        <v>0</v>
+      </c>
+      <c r="F33" s="42">
         <v>307</v>
       </c>
-      <c r="G33" s="44">
+      <c r="G33" s="42">
         <v>307</v>
       </c>
-      <c r="H33" s="44">
-        <v>0</v>
-      </c>
-      <c r="L33" s="19" t="s">
+      <c r="H33" s="42">
+        <v>0</v>
+      </c>
+      <c r="L33" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="M33" s="19" t="s">
+      <c r="M33" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="N33" s="20">
+      <c r="N33" s="18">
         <v>267411</v>
       </c>
-      <c r="O33" s="20">
+      <c r="O33" s="18">
         <v>13006</v>
       </c>
-      <c r="P33" s="20"/>
-      <c r="Q33" s="20"/>
-      <c r="R33" s="19"/>
+      <c r="P33" s="18"/>
+      <c r="Q33" s="18"/>
+      <c r="R33" s="17"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B34" s="43" t="s">
+      <c r="B34" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="C34" s="44">
+      <c r="C34" s="42">
         <v>585431</v>
       </c>
-      <c r="D34" s="44">
+      <c r="D34" s="42">
         <v>515822</v>
       </c>
-      <c r="E34" s="44">
+      <c r="E34" s="42">
         <v>69609</v>
       </c>
-      <c r="F34" s="44">
+      <c r="F34" s="42">
         <v>23113</v>
       </c>
-      <c r="G34" s="44">
+      <c r="G34" s="42">
         <v>13685</v>
       </c>
-      <c r="H34" s="44">
+      <c r="H34" s="42">
         <v>9428</v>
       </c>
-      <c r="L34" s="19" t="s">
+      <c r="L34" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="M34" s="19" t="s">
+      <c r="M34" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="N34" s="20"/>
-      <c r="O34" s="20">
+      <c r="N34" s="18"/>
+      <c r="O34" s="18">
         <v>11889</v>
       </c>
-      <c r="P34" s="20">
+      <c r="P34" s="18">
         <v>13223</v>
       </c>
-      <c r="Q34" s="19"/>
-      <c r="R34" s="19"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="17"/>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B35" s="43" t="s">
+      <c r="B35" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="C35" s="44">
+      <c r="C35" s="42">
         <v>2285</v>
       </c>
-      <c r="D35" s="44">
+      <c r="D35" s="42">
         <v>2285</v>
       </c>
-      <c r="E35" s="44">
-        <v>0</v>
-      </c>
-      <c r="F35" s="44">
+      <c r="E35" s="42">
+        <v>0</v>
+      </c>
+      <c r="F35" s="42">
         <v>11379</v>
       </c>
-      <c r="G35" s="44">
+      <c r="G35" s="42">
         <v>11379</v>
       </c>
-      <c r="H35" s="44">
-        <v>0</v>
-      </c>
-      <c r="L35" s="19" t="s">
+      <c r="H35" s="42">
+        <v>0</v>
+      </c>
+      <c r="L35" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="M35" s="19" t="s">
+      <c r="M35" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="N35" s="20">
+      <c r="N35" s="18">
         <v>30821</v>
       </c>
-      <c r="O35" s="20">
+      <c r="O35" s="18">
         <v>190728</v>
       </c>
-      <c r="P35" s="20"/>
-      <c r="Q35" s="19"/>
-      <c r="R35" s="19"/>
+      <c r="P35" s="18"/>
+      <c r="Q35" s="17"/>
+      <c r="R35" s="17"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B36" s="43" t="s">
+      <c r="B36" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="44">
+      <c r="C36" s="42">
         <v>10720</v>
       </c>
-      <c r="D36" s="44">
+      <c r="D36" s="42">
         <v>10720</v>
       </c>
-      <c r="E36" s="44">
-        <v>0</v>
-      </c>
-      <c r="F36" s="44">
-        <v>0</v>
-      </c>
-      <c r="G36" s="44">
-        <v>0</v>
-      </c>
-      <c r="H36" s="44">
-        <v>0</v>
-      </c>
-      <c r="L36" s="19" t="s">
+      <c r="E36" s="42">
+        <v>0</v>
+      </c>
+      <c r="F36" s="42">
+        <v>0</v>
+      </c>
+      <c r="G36" s="42">
+        <v>0</v>
+      </c>
+      <c r="H36" s="42">
+        <v>0</v>
+      </c>
+      <c r="L36" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="M36" s="19" t="s">
+      <c r="M36" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="N36" s="20">
+      <c r="N36" s="18">
         <v>310398</v>
       </c>
-      <c r="O36" s="20">
+      <c r="O36" s="18">
         <v>239120</v>
       </c>
-      <c r="P36" s="20">
+      <c r="P36" s="18">
         <v>5790</v>
       </c>
-      <c r="Q36" s="20">
+      <c r="Q36" s="18">
         <v>5710</v>
       </c>
-      <c r="R36" s="19"/>
+      <c r="R36" s="17"/>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B37" s="43" t="s">
+      <c r="B37" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="C37" s="44">
+      <c r="C37" s="42">
         <v>48884</v>
       </c>
-      <c r="D37" s="44">
+      <c r="D37" s="42">
         <v>48331</v>
       </c>
-      <c r="E37" s="44">
+      <c r="E37" s="42">
         <v>553</v>
       </c>
-      <c r="F37" s="44">
-        <v>0</v>
-      </c>
-      <c r="G37" s="44">
-        <v>0</v>
-      </c>
-      <c r="H37" s="44">
-        <v>0</v>
-      </c>
-      <c r="L37" s="18" t="s">
+      <c r="F37" s="42">
+        <v>0</v>
+      </c>
+      <c r="G37" s="42">
+        <v>0</v>
+      </c>
+      <c r="H37" s="42">
+        <v>0</v>
+      </c>
+      <c r="L37" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="M37" s="18" t="s">
+      <c r="M37" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="N37" s="22">
+      <c r="N37" s="20">
         <v>1670999</v>
       </c>
-      <c r="O37" s="22">
+      <c r="O37" s="20">
         <v>576313</v>
       </c>
-      <c r="P37" s="22">
+      <c r="P37" s="20">
         <v>33993</v>
       </c>
-      <c r="Q37" s="22">
+      <c r="Q37" s="20">
         <v>5710</v>
       </c>
-      <c r="R37" s="18"/>
+      <c r="R37" s="16"/>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B38" s="43" t="s">
+      <c r="B38" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="C38" s="44">
+      <c r="C38" s="42">
         <v>475751</v>
       </c>
-      <c r="D38" s="44">
+      <c r="D38" s="42">
         <v>555751</v>
       </c>
-      <c r="E38" s="26">
+      <c r="E38" s="24">
         <v>-80000</v>
       </c>
-      <c r="F38" s="44">
+      <c r="F38" s="42">
         <v>44302</v>
       </c>
-      <c r="G38" s="44">
+      <c r="G38" s="42">
         <v>44302</v>
       </c>
-      <c r="H38" s="44">
-        <v>0</v>
-      </c>
-      <c r="L38" s="19" t="s">
+      <c r="H38" s="42">
+        <v>0</v>
+      </c>
+      <c r="L38" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="M38" s="19" t="s">
+      <c r="M38" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="N38" s="20">
+      <c r="N38" s="18">
         <v>326249</v>
       </c>
-      <c r="O38" s="20">
+      <c r="O38" s="18">
         <v>95785</v>
       </c>
-      <c r="P38" s="20"/>
-      <c r="Q38" s="19"/>
-      <c r="R38" s="20"/>
+      <c r="P38" s="18"/>
+      <c r="Q38" s="17"/>
+      <c r="R38" s="18"/>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B39" s="43" t="s">
+      <c r="B39" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="C39" s="44">
+      <c r="C39" s="42">
         <v>1403924</v>
       </c>
-      <c r="D39" s="44">
+      <c r="D39" s="42">
         <v>1313451</v>
       </c>
-      <c r="E39" s="44">
+      <c r="E39" s="42">
         <v>90473</v>
       </c>
-      <c r="F39" s="44">
+      <c r="F39" s="42">
         <v>44160</v>
       </c>
-      <c r="G39" s="44">
+      <c r="G39" s="42">
         <v>44160</v>
       </c>
-      <c r="H39" s="44">
-        <v>0</v>
-      </c>
-      <c r="L39" s="19" t="s">
+      <c r="H39" s="42">
+        <v>0</v>
+      </c>
+      <c r="L39" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="M39" s="19" t="s">
+      <c r="M39" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="N39" s="20">
+      <c r="N39" s="18">
         <v>67011</v>
       </c>
-      <c r="O39" s="19">
+      <c r="O39" s="17">
         <v>282069</v>
       </c>
-      <c r="P39" s="19">
+      <c r="P39" s="17">
         <v>6655</v>
       </c>
-      <c r="Q39" s="19"/>
-      <c r="R39" s="19"/>
+      <c r="Q39" s="17"/>
+      <c r="R39" s="17"/>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B40" s="43" t="s">
+      <c r="B40" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="C40" s="44">
+      <c r="C40" s="42">
         <v>2500</v>
       </c>
-      <c r="D40" s="44">
+      <c r="D40" s="42">
         <v>2500</v>
       </c>
-      <c r="E40" s="44">
-        <v>0</v>
-      </c>
-      <c r="F40" s="44">
-        <v>0</v>
-      </c>
-      <c r="G40" s="44">
-        <v>0</v>
-      </c>
-      <c r="H40" s="44">
-        <v>0</v>
-      </c>
-      <c r="L40" s="19" t="s">
+      <c r="E40" s="42">
+        <v>0</v>
+      </c>
+      <c r="F40" s="42">
+        <v>0</v>
+      </c>
+      <c r="G40" s="42">
+        <v>0</v>
+      </c>
+      <c r="H40" s="42">
+        <v>0</v>
+      </c>
+      <c r="L40" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="M40" s="19" t="s">
+      <c r="M40" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="N40" s="20">
+      <c r="N40" s="18">
         <v>1021277</v>
       </c>
-      <c r="O40" s="19">
+      <c r="O40" s="17">
         <v>1017547</v>
       </c>
-      <c r="P40" s="19">
+      <c r="P40" s="17">
         <v>1341221</v>
       </c>
-      <c r="Q40" s="19">
+      <c r="Q40" s="17">
         <v>78387</v>
       </c>
-      <c r="R40" s="19"/>
+      <c r="R40" s="17"/>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B41" s="43" t="s">
+      <c r="B41" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="C41" s="44">
-        <v>0</v>
-      </c>
-      <c r="D41" s="44">
-        <v>0</v>
-      </c>
-      <c r="E41" s="44">
-        <v>0</v>
-      </c>
-      <c r="F41" s="44">
+      <c r="C41" s="42">
+        <v>0</v>
+      </c>
+      <c r="D41" s="42">
+        <v>0</v>
+      </c>
+      <c r="E41" s="42">
+        <v>0</v>
+      </c>
+      <c r="F41" s="42">
         <v>11889</v>
       </c>
-      <c r="G41" s="44">
+      <c r="G41" s="42">
         <v>11889</v>
       </c>
-      <c r="H41" s="44">
-        <v>0</v>
-      </c>
-      <c r="L41" s="18" t="s">
+      <c r="H41" s="42">
+        <v>0</v>
+      </c>
+      <c r="L41" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="M41" s="18" t="s">
+      <c r="M41" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="N41" s="22">
+      <c r="N41" s="20">
         <v>1414537</v>
       </c>
-      <c r="O41" s="22">
+      <c r="O41" s="20">
         <v>1395400</v>
       </c>
-      <c r="P41" s="22">
+      <c r="P41" s="20">
         <v>1347876</v>
       </c>
-      <c r="Q41" s="22">
+      <c r="Q41" s="20">
         <v>78387</v>
       </c>
-      <c r="R41" s="22"/>
+      <c r="R41" s="20"/>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B42" s="43" t="s">
+      <c r="B42" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="C42" s="44">
+      <c r="C42" s="42">
         <v>55588</v>
       </c>
-      <c r="D42" s="44">
+      <c r="D42" s="42">
         <v>53638</v>
       </c>
-      <c r="E42" s="44">
+      <c r="E42" s="42">
         <v>1950</v>
       </c>
-      <c r="F42" s="44">
+      <c r="F42" s="42">
         <v>7350</v>
       </c>
-      <c r="G42" s="44">
-        <v>0</v>
-      </c>
-      <c r="H42" s="44">
+      <c r="G42" s="42">
+        <v>0</v>
+      </c>
+      <c r="H42" s="42">
         <v>7350</v>
       </c>
-      <c r="L42" s="18" t="s">
+      <c r="L42" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="M42" s="18" t="s">
+      <c r="M42" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="N42" s="22">
+      <c r="N42" s="20">
         <v>6569317</v>
       </c>
-      <c r="O42" s="22">
+      <c r="O42" s="20">
         <v>2644544</v>
       </c>
-      <c r="P42" s="22">
+      <c r="P42" s="20">
         <v>1808244</v>
       </c>
-      <c r="Q42" s="22">
+      <c r="Q42" s="20">
         <v>299098</v>
       </c>
-      <c r="R42" s="22">
+      <c r="R42" s="20">
         <v>1993</v>
       </c>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B43" s="43" t="s">
+      <c r="B43" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="C43" s="44">
+      <c r="C43" s="42">
         <v>30821</v>
       </c>
-      <c r="D43" s="44">
+      <c r="D43" s="42">
         <v>30821</v>
       </c>
-      <c r="E43" s="44">
-        <v>0</v>
-      </c>
-      <c r="F43" s="44">
+      <c r="E43" s="42">
+        <v>0</v>
+      </c>
+      <c r="F43" s="42">
         <v>190728</v>
       </c>
-      <c r="G43" s="44">
+      <c r="G43" s="42">
         <v>190728</v>
       </c>
-      <c r="H43" s="44">
+      <c r="H43" s="42">
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B44" s="43" t="s">
+      <c r="B44" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="C44" s="44">
+      <c r="C44" s="42">
         <v>53962</v>
       </c>
-      <c r="D44" s="44">
+      <c r="D44" s="42">
         <v>38198</v>
       </c>
-      <c r="E44" s="44">
+      <c r="E44" s="42">
         <v>15764</v>
       </c>
-      <c r="F44" s="44">
+      <c r="F44" s="42">
         <v>7943</v>
       </c>
-      <c r="G44" s="44">
+      <c r="G44" s="42">
         <v>7943</v>
       </c>
-      <c r="H44" s="44">
+      <c r="H44" s="42">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="43" t="s">
+      <c r="B45" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="C45" s="44">
+      <c r="C45" s="42">
         <v>545673</v>
       </c>
-      <c r="D45" s="44">
+      <c r="D45" s="42">
         <v>545669</v>
       </c>
-      <c r="E45" s="44">
+      <c r="E45" s="42">
         <v>4</v>
       </c>
-      <c r="F45" s="44">
+      <c r="F45" s="42">
         <v>669047</v>
       </c>
-      <c r="G45" s="44">
+      <c r="G45" s="42">
         <v>669720</v>
       </c>
-      <c r="H45" s="26">
+      <c r="H45" s="24">
         <v>-673</v>
       </c>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B46" s="43" t="s">
+      <c r="B46" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="C46" s="44">
+      <c r="C46" s="42">
         <v>96589</v>
       </c>
-      <c r="D46" s="44">
+      <c r="D46" s="42">
         <v>96589</v>
       </c>
-      <c r="E46" s="44">
-        <v>0</v>
-      </c>
-      <c r="F46" s="44">
+      <c r="E46" s="42">
+        <v>0</v>
+      </c>
+      <c r="F46" s="42">
         <v>24323</v>
       </c>
-      <c r="G46" s="44">
+      <c r="G46" s="42">
         <v>24323</v>
       </c>
-      <c r="H46" s="44">
+      <c r="H46" s="42">
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B47" s="43" t="s">
+      <c r="B47" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="C47" s="44">
+      <c r="C47" s="42">
         <v>4472</v>
       </c>
-      <c r="D47" s="44">
+      <c r="D47" s="42">
         <v>4472</v>
       </c>
-      <c r="E47" s="44">
-        <v>0</v>
-      </c>
-      <c r="F47" s="44">
+      <c r="E47" s="42">
+        <v>0</v>
+      </c>
+      <c r="F47" s="42">
         <v>15969</v>
       </c>
-      <c r="G47" s="44">
+      <c r="G47" s="42">
         <v>15969</v>
       </c>
-      <c r="H47" s="44">
+      <c r="H47" s="42">
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B48" s="43" t="s">
+      <c r="B48" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="C48" s="44">
+      <c r="C48" s="42">
         <v>1025572</v>
       </c>
-      <c r="D48" s="44">
+      <c r="D48" s="42">
         <v>1025571</v>
       </c>
-      <c r="E48" s="44">
+      <c r="E48" s="42">
         <v>1</v>
       </c>
-      <c r="F48" s="44">
+      <c r="F48" s="42">
         <v>1032250</v>
       </c>
-      <c r="G48" s="44">
+      <c r="G48" s="42">
         <v>1032250</v>
       </c>
-      <c r="H48" s="44">
+      <c r="H48" s="42">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B49" s="43" t="s">
+      <c r="B49" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="C49" s="44">
+      <c r="C49" s="42">
         <v>9112</v>
       </c>
-      <c r="D49" s="44">
+      <c r="D49" s="42">
         <v>12238</v>
       </c>
-      <c r="E49" s="26">
+      <c r="E49" s="24">
         <v>-3126</v>
       </c>
-      <c r="F49" s="44">
-        <v>0</v>
-      </c>
-      <c r="G49" s="44">
-        <v>0</v>
-      </c>
-      <c r="H49" s="44">
+      <c r="F49" s="42">
+        <v>0</v>
+      </c>
+      <c r="G49" s="42">
+        <v>0</v>
+      </c>
+      <c r="H49" s="42">
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B50" s="42" t="s">
+      <c r="B50" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="C50" s="45">
+      <c r="C50" s="43">
         <v>6569317</v>
       </c>
-      <c r="D50" s="45">
+      <c r="D50" s="43">
         <v>6456328</v>
       </c>
-      <c r="E50" s="45">
+      <c r="E50" s="43">
         <v>112990</v>
       </c>
-      <c r="F50" s="45">
+      <c r="F50" s="43">
         <v>2644544</v>
       </c>
-      <c r="G50" s="45">
+      <c r="G50" s="43">
         <v>2613011</v>
       </c>
-      <c r="H50" s="45">
+      <c r="H50" s="43">
         <v>31534</v>
       </c>
-      <c r="L50" s="27"/>
-      <c r="M50" s="27"/>
-      <c r="N50" s="27"/>
-      <c r="O50" s="27"/>
-      <c r="P50" s="27"/>
-      <c r="Q50" s="27"/>
-      <c r="R50" s="27"/>
+      <c r="L50" s="25"/>
+      <c r="M50" s="25"/>
+      <c r="N50" s="25"/>
+      <c r="O50" s="25"/>
+      <c r="P50" s="25"/>
+      <c r="Q50" s="25"/>
+      <c r="R50" s="25"/>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="L51" s="27"/>
-      <c r="M51" s="27"/>
-      <c r="N51" s="27"/>
-      <c r="O51" s="27"/>
-      <c r="P51" s="27"/>
-      <c r="Q51" s="27"/>
-      <c r="R51" s="27"/>
+      <c r="L51" s="25"/>
+      <c r="M51" s="25"/>
+      <c r="N51" s="25"/>
+      <c r="O51" s="25"/>
+      <c r="P51" s="25"/>
+      <c r="Q51" s="25"/>
+      <c r="R51" s="25"/>
     </row>
     <row r="52" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="L52" s="27"/>
-      <c r="M52" s="28" t="s">
+      <c r="L52" s="25"/>
+      <c r="M52" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="N52" s="27"/>
-      <c r="O52" s="27"/>
-      <c r="P52" s="27"/>
-      <c r="Q52" s="27"/>
-      <c r="R52" s="27"/>
+      <c r="N52" s="25"/>
+      <c r="O52" s="25"/>
+      <c r="P52" s="25"/>
+      <c r="Q52" s="25"/>
+      <c r="R52" s="25"/>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B53" s="27"/>
-      <c r="C53" s="27"/>
-      <c r="D53" s="27"/>
-      <c r="E53" s="27"/>
-      <c r="F53" s="27"/>
-      <c r="G53" s="27"/>
-      <c r="H53" s="27"/>
-      <c r="L53" s="27"/>
-      <c r="M53" s="29" t="s">
+      <c r="B53" s="25"/>
+      <c r="C53" s="25"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="25"/>
+      <c r="G53" s="25"/>
+      <c r="H53" s="25"/>
+      <c r="L53" s="25"/>
+      <c r="M53" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="N53" s="29" t="s">
+      <c r="N53" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="O53" s="29" t="s">
+      <c r="O53" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="P53" s="29" t="s">
+      <c r="P53" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="Q53" s="29" t="s">
+      <c r="Q53" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="R53" s="27"/>
+      <c r="R53" s="25"/>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B54" s="27"/>
-      <c r="C54" s="27"/>
-      <c r="D54" s="27"/>
-      <c r="E54" s="27"/>
-      <c r="F54" s="27"/>
-      <c r="G54" s="27"/>
-      <c r="H54" s="27"/>
-      <c r="L54" s="27"/>
-      <c r="M54" s="30" t="s">
+      <c r="B54" s="25"/>
+      <c r="C54" s="25"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="25"/>
+      <c r="F54" s="25"/>
+      <c r="G54" s="25"/>
+      <c r="H54" s="25"/>
+      <c r="L54" s="25"/>
+      <c r="M54" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="N54" s="30">
+      <c r="N54" s="28">
         <v>3000</v>
       </c>
-      <c r="O54" s="30">
+      <c r="O54" s="28">
         <v>17604</v>
       </c>
-      <c r="P54" s="30">
+      <c r="P54" s="28">
         <v>2396</v>
       </c>
-      <c r="Q54" s="30">
-        <v>0</v>
-      </c>
-      <c r="R54" s="27"/>
+      <c r="Q54" s="28">
+        <v>0</v>
+      </c>
+      <c r="R54" s="25"/>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B55" s="27"/>
-      <c r="C55" s="27"/>
-      <c r="D55" s="27"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="27"/>
-      <c r="H55" s="27"/>
-      <c r="L55" s="27"/>
-      <c r="M55" s="30" t="s">
+      <c r="B55" s="25"/>
+      <c r="C55" s="25"/>
+      <c r="D55" s="25"/>
+      <c r="E55" s="25"/>
+      <c r="F55" s="25"/>
+      <c r="G55" s="25"/>
+      <c r="H55" s="25"/>
+      <c r="L55" s="25"/>
+      <c r="M55" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="N55" s="30">
+      <c r="N55" s="28">
         <v>4000</v>
       </c>
-      <c r="O55" s="30">
+      <c r="O55" s="28">
         <v>1000188</v>
       </c>
-      <c r="P55" s="30">
+      <c r="P55" s="28">
         <v>1015205</v>
       </c>
-      <c r="Q55" s="30">
+      <c r="Q55" s="28">
         <v>1341221</v>
       </c>
-      <c r="R55" s="27"/>
+      <c r="R55" s="25"/>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="L56" s="27"/>
-      <c r="M56" s="29" t="s">
+      <c r="L56" s="25"/>
+      <c r="M56" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="N56" s="29">
+      <c r="N56" s="27">
         <v>7000</v>
       </c>
-      <c r="O56" s="29">
+      <c r="O56" s="27">
         <v>1017791</v>
       </c>
-      <c r="P56" s="29">
+      <c r="P56" s="27">
         <v>1017601</v>
       </c>
-      <c r="Q56" s="29">
+      <c r="Q56" s="27">
         <v>1341221</v>
       </c>
-      <c r="R56" s="27"/>
+      <c r="R56" s="25"/>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="L57" s="27"/>
-      <c r="M57" s="27"/>
-      <c r="N57" s="27"/>
-      <c r="O57" s="27"/>
-      <c r="P57" s="27"/>
-      <c r="Q57" s="27"/>
-      <c r="R57" s="27"/>
+      <c r="L57" s="25"/>
+      <c r="M57" s="25"/>
+      <c r="N57" s="25"/>
+      <c r="O57" s="25"/>
+      <c r="P57" s="25"/>
+      <c r="Q57" s="25"/>
+      <c r="R57" s="25"/>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="L58" s="27"/>
-      <c r="M58" s="27"/>
-      <c r="N58" s="27"/>
-      <c r="O58" s="27"/>
-      <c r="P58" s="27"/>
-      <c r="Q58" s="27"/>
-      <c r="R58" s="27"/>
-    </row>
-    <row r="59" spans="1:18" s="48" customFormat="1" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="46" t="s">
+      <c r="L58" s="25"/>
+      <c r="M58" s="25"/>
+      <c r="N58" s="25"/>
+      <c r="O58" s="25"/>
+      <c r="P58" s="25"/>
+      <c r="Q58" s="25"/>
+      <c r="R58" s="25"/>
+    </row>
+    <row r="59" spans="1:18" s="46" customFormat="1" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="B59" s="46" t="s">
+      <c r="B59" s="44" t="s">
         <v>95</v>
       </c>
-      <c r="C59" s="47" t="s">
+      <c r="C59" s="45" t="s">
         <v>117</v>
       </c>
-      <c r="D59" s="46" t="s">
+      <c r="D59" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="L59" s="49"/>
-      <c r="M59" s="49"/>
-      <c r="N59" s="49"/>
-      <c r="O59" s="49"/>
-      <c r="P59" s="49"/>
-      <c r="Q59" s="49"/>
-      <c r="R59" s="49"/>
+      <c r="L59" s="47"/>
+      <c r="M59" s="47"/>
+      <c r="N59" s="47"/>
+      <c r="O59" s="47"/>
+      <c r="P59" s="47"/>
+      <c r="Q59" s="47"/>
+      <c r="R59" s="47"/>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
@@ -3161,19 +3169,19 @@
       </c>
       <c r="C60" s="5">
         <f>(B60/20)*$E$13</f>
-        <v>1474</v>
+        <v>1742</v>
       </c>
       <c r="D60" s="5">
         <f t="shared" ref="D60:D67" si="2">B60*$I$13/20</f>
         <v>1675</v>
       </c>
-      <c r="L60" s="27"/>
-      <c r="M60" s="27"/>
-      <c r="N60" s="27"/>
-      <c r="O60" s="27"/>
-      <c r="P60" s="27"/>
-      <c r="Q60" s="27"/>
-      <c r="R60" s="27"/>
+      <c r="L60" s="25"/>
+      <c r="M60" s="25"/>
+      <c r="N60" s="25"/>
+      <c r="O60" s="25"/>
+      <c r="P60" s="25"/>
+      <c r="Q60" s="25"/>
+      <c r="R60" s="25"/>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
@@ -3184,19 +3192,19 @@
       </c>
       <c r="C61" s="5">
         <f t="shared" ref="C61:C67" si="3">(B61/20)*$E$13</f>
-        <v>668.8</v>
+        <v>790.4</v>
       </c>
       <c r="D61" s="5">
         <f t="shared" si="2"/>
         <v>760</v>
       </c>
-      <c r="L61" s="27"/>
-      <c r="M61" s="27"/>
-      <c r="N61" s="27"/>
-      <c r="O61" s="27"/>
-      <c r="P61" s="27"/>
-      <c r="Q61" s="27"/>
-      <c r="R61" s="27"/>
+      <c r="L61" s="25"/>
+      <c r="M61" s="25"/>
+      <c r="N61" s="25"/>
+      <c r="O61" s="25"/>
+      <c r="P61" s="25"/>
+      <c r="Q61" s="25"/>
+      <c r="R61" s="25"/>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
@@ -3207,19 +3215,19 @@
       </c>
       <c r="C62" s="5">
         <f t="shared" si="3"/>
-        <v>1673.1</v>
+        <v>1977.3</v>
       </c>
       <c r="D62" s="5">
         <f t="shared" si="2"/>
         <v>1901.25</v>
       </c>
-      <c r="L62" s="27"/>
-      <c r="M62" s="27"/>
-      <c r="N62" s="27"/>
-      <c r="O62" s="27"/>
-      <c r="P62" s="27"/>
-      <c r="Q62" s="27"/>
-      <c r="R62" s="27"/>
+      <c r="L62" s="25"/>
+      <c r="M62" s="25"/>
+      <c r="N62" s="25"/>
+      <c r="O62" s="25"/>
+      <c r="P62" s="25"/>
+      <c r="Q62" s="25"/>
+      <c r="R62" s="25"/>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
@@ -3230,19 +3238,19 @@
       </c>
       <c r="C63" s="5">
         <f t="shared" si="3"/>
-        <v>1377.2</v>
+        <v>1627.6000000000001</v>
       </c>
       <c r="D63" s="5">
         <f t="shared" si="2"/>
         <v>1565</v>
       </c>
-      <c r="L63" s="27"/>
-      <c r="M63" s="27"/>
-      <c r="N63" s="27"/>
-      <c r="O63" s="27"/>
-      <c r="P63" s="27"/>
-      <c r="Q63" s="27"/>
-      <c r="R63" s="27"/>
+      <c r="L63" s="25"/>
+      <c r="M63" s="25"/>
+      <c r="N63" s="25"/>
+      <c r="O63" s="25"/>
+      <c r="P63" s="25"/>
+      <c r="Q63" s="25"/>
+      <c r="R63" s="25"/>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
@@ -3253,19 +3261,19 @@
       </c>
       <c r="C64" s="5">
         <f t="shared" si="3"/>
-        <v>1331</v>
+        <v>1573</v>
       </c>
       <c r="D64" s="5">
         <f t="shared" si="2"/>
         <v>1512.5</v>
       </c>
-      <c r="L64" s="27"/>
-      <c r="M64" s="27"/>
-      <c r="N64" s="27"/>
-      <c r="O64" s="27"/>
-      <c r="P64" s="27"/>
-      <c r="Q64" s="27"/>
-      <c r="R64" s="27"/>
+      <c r="L64" s="25"/>
+      <c r="M64" s="25"/>
+      <c r="N64" s="25"/>
+      <c r="O64" s="25"/>
+      <c r="P64" s="25"/>
+      <c r="Q64" s="25"/>
+      <c r="R64" s="25"/>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
@@ -3276,19 +3284,19 @@
       </c>
       <c r="C65" s="5">
         <f t="shared" si="3"/>
-        <v>2376</v>
+        <v>2808</v>
       </c>
       <c r="D65" s="5">
         <f t="shared" si="2"/>
         <v>2700</v>
       </c>
-      <c r="L65" s="27"/>
-      <c r="M65" s="27"/>
-      <c r="N65" s="27"/>
-      <c r="O65" s="27"/>
-      <c r="P65" s="27"/>
-      <c r="Q65" s="27"/>
-      <c r="R65" s="27"/>
+      <c r="L65" s="25"/>
+      <c r="M65" s="25"/>
+      <c r="N65" s="25"/>
+      <c r="O65" s="25"/>
+      <c r="P65" s="25"/>
+      <c r="Q65" s="25"/>
+      <c r="R65" s="25"/>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
@@ -3299,19 +3307,19 @@
       </c>
       <c r="C66" s="5">
         <f t="shared" si="3"/>
-        <v>871.2</v>
+        <v>1029.6000000000001</v>
       </c>
       <c r="D66" s="5">
         <f t="shared" si="2"/>
         <v>990</v>
       </c>
-      <c r="L66" s="27"/>
-      <c r="M66" s="27"/>
-      <c r="N66" s="27"/>
-      <c r="O66" s="27"/>
-      <c r="P66" s="27"/>
-      <c r="Q66" s="27"/>
-      <c r="R66" s="27"/>
+      <c r="L66" s="25"/>
+      <c r="M66" s="25"/>
+      <c r="N66" s="25"/>
+      <c r="O66" s="25"/>
+      <c r="P66" s="25"/>
+      <c r="Q66" s="25"/>
+      <c r="R66" s="25"/>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
@@ -3322,66 +3330,66 @@
       </c>
       <c r="C67" s="5">
         <f t="shared" si="3"/>
-        <v>9771.2999999999993</v>
+        <v>11547.9</v>
       </c>
       <c r="D67" s="5">
         <f t="shared" si="2"/>
         <v>11103.75</v>
       </c>
-      <c r="L67" s="27"/>
-      <c r="M67" s="27"/>
-      <c r="N67" s="27"/>
-      <c r="O67" s="27"/>
-      <c r="P67" s="27"/>
-      <c r="Q67" s="27"/>
-      <c r="R67" s="27"/>
+      <c r="L67" s="25"/>
+      <c r="M67" s="25"/>
+      <c r="N67" s="25"/>
+      <c r="O67" s="25"/>
+      <c r="P67" s="25"/>
+      <c r="Q67" s="25"/>
+      <c r="R67" s="25"/>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="L68" s="27"/>
-      <c r="M68" s="27"/>
-      <c r="N68" s="27"/>
-      <c r="O68" s="27"/>
-      <c r="P68" s="27"/>
-      <c r="Q68" s="27"/>
-      <c r="R68" s="27"/>
+      <c r="L68" s="25"/>
+      <c r="M68" s="25"/>
+      <c r="N68" s="25"/>
+      <c r="O68" s="25"/>
+      <c r="P68" s="25"/>
+      <c r="Q68" s="25"/>
+      <c r="R68" s="25"/>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="C69" s="11"/>
-      <c r="D69" s="11"/>
-      <c r="L69" s="27"/>
-      <c r="M69" s="27"/>
-      <c r="N69" s="27"/>
-      <c r="O69" s="27"/>
-      <c r="P69" s="27"/>
-      <c r="Q69" s="27"/>
-      <c r="R69" s="27"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="9"/>
+      <c r="L69" s="25"/>
+      <c r="M69" s="25"/>
+      <c r="N69" s="25"/>
+      <c r="O69" s="25"/>
+      <c r="P69" s="25"/>
+      <c r="Q69" s="25"/>
+      <c r="R69" s="25"/>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="L70" s="27"/>
-      <c r="M70" s="27"/>
-      <c r="N70" s="27"/>
-      <c r="O70" s="27"/>
-      <c r="P70" s="27"/>
-      <c r="Q70" s="27"/>
-      <c r="R70" s="27"/>
+      <c r="L70" s="25"/>
+      <c r="M70" s="25"/>
+      <c r="N70" s="25"/>
+      <c r="O70" s="25"/>
+      <c r="P70" s="25"/>
+      <c r="Q70" s="25"/>
+      <c r="R70" s="25"/>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="L71" s="27"/>
-      <c r="M71" s="27"/>
-      <c r="N71" s="27"/>
-      <c r="O71" s="27"/>
-      <c r="P71" s="27"/>
-      <c r="Q71" s="27"/>
-      <c r="R71" s="27"/>
+      <c r="L71" s="25"/>
+      <c r="M71" s="25"/>
+      <c r="N71" s="25"/>
+      <c r="O71" s="25"/>
+      <c r="P71" s="25"/>
+      <c r="Q71" s="25"/>
+      <c r="R71" s="25"/>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="L72" s="27"/>
-      <c r="M72" s="27"/>
-      <c r="N72" s="27"/>
-      <c r="O72" s="27"/>
-      <c r="P72" s="27"/>
-      <c r="Q72" s="27"/>
-      <c r="R72" s="27"/>
+      <c r="L72" s="25"/>
+      <c r="M72" s="25"/>
+      <c r="N72" s="25"/>
+      <c r="O72" s="25"/>
+      <c r="P72" s="25"/>
+      <c r="Q72" s="25"/>
+      <c r="R72" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -3397,7 +3405,7 @@
     <mergeCell ref="A3:A4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="51" fitToHeight="0" orientation="landscape"/>
+  <pageSetup scale="51" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3407,258 +3415,258 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="29" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="32">
+      <c r="C2" s="30">
         <v>456</v>
       </c>
-      <c r="D2" s="32">
+      <c r="D2" s="30">
         <v>742</v>
       </c>
-      <c r="E2" s="32">
+      <c r="E2" s="30">
         <v>286</v>
       </c>
-      <c r="F2" s="32">
+      <c r="F2" s="30">
         <v>1346</v>
       </c>
-      <c r="G2" s="32">
+      <c r="G2" s="30">
         <v>1420</v>
       </c>
-      <c r="H2" s="32">
+      <c r="H2" s="30">
         <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="32">
+      <c r="C3" s="30">
         <v>32</v>
       </c>
-      <c r="D3" s="32">
+      <c r="D3" s="30">
         <v>34</v>
       </c>
-      <c r="E3" s="32">
+      <c r="E3" s="30">
         <v>2</v>
       </c>
-      <c r="F3" s="32">
+      <c r="F3" s="30">
         <v>406</v>
       </c>
-      <c r="G3" s="32">
+      <c r="G3" s="30">
         <v>446</v>
       </c>
-      <c r="H3" s="32">
+      <c r="H3" s="30">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="32">
+      <c r="C4" s="30">
         <v>655</v>
       </c>
-      <c r="D4" s="32">
+      <c r="D4" s="30">
         <v>702</v>
       </c>
-      <c r="E4" s="32">
+      <c r="E4" s="30">
         <v>47</v>
       </c>
-      <c r="F4" s="32">
+      <c r="F4" s="30">
         <v>976</v>
       </c>
-      <c r="G4" s="32">
+      <c r="G4" s="30">
         <v>1195</v>
       </c>
-      <c r="H4" s="32">
+      <c r="H4" s="30">
         <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="32">
+      <c r="C5" s="30">
         <v>-302</v>
       </c>
-      <c r="D5" s="32">
+      <c r="D5" s="30">
         <v>-409</v>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="30">
         <v>-107</v>
       </c>
-      <c r="F5" s="32">
+      <c r="F5" s="30">
         <v>-452</v>
       </c>
-      <c r="G5" s="32">
+      <c r="G5" s="30">
         <v>-438</v>
       </c>
-      <c r="H5" s="32">
+      <c r="H5" s="30">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="30">
         <v>448</v>
       </c>
-      <c r="D6" s="32">
+      <c r="D6" s="30">
         <v>539</v>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="30">
         <v>91</v>
       </c>
-      <c r="F6" s="32">
+      <c r="F6" s="30">
         <v>1299</v>
       </c>
-      <c r="G6" s="32">
+      <c r="G6" s="30">
         <v>1378</v>
       </c>
-      <c r="H6" s="32">
+      <c r="H6" s="30">
         <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="30">
         <v>1047</v>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="30">
         <v>1231</v>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="30">
         <v>184</v>
       </c>
-      <c r="F7" s="32">
+      <c r="F7" s="30">
         <v>1679</v>
       </c>
-      <c r="G7" s="32">
+      <c r="G7" s="30">
         <v>1860</v>
       </c>
-      <c r="H7" s="32">
+      <c r="H7" s="30">
         <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="30">
         <v>1031</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="30">
         <v>1031</v>
       </c>
-      <c r="E8" s="32">
-        <v>0</v>
-      </c>
-      <c r="F8" s="32">
+      <c r="E8" s="30">
+        <v>0</v>
+      </c>
+      <c r="F8" s="30">
         <v>833</v>
       </c>
-      <c r="G8" s="32">
+      <c r="G8" s="30">
         <v>872</v>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="30">
         <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="30">
         <v>3367</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="30">
         <v>3870</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="30">
         <v>503</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="30">
         <v>6087</v>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="30">
         <v>6734</v>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="30">
         <v>647</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="32"/>
-      <c r="B10" s="32"/>
-      <c r="C10" s="32" t="s">
+      <c r="A10" s="30"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="30">
         <v>11336</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F10" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="G10" s="32">
+      <c r="G10" s="30">
         <v>9592</v>
       </c>
-      <c r="H10" s="32" t="s">
+      <c r="H10" s="30" t="s">
         <v>107</v>
       </c>
     </row>
@@ -3673,290 +3681,290 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="29" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="32">
+      <c r="C2" s="30">
         <v>-48</v>
       </c>
-      <c r="D2" s="32">
+      <c r="D2" s="30">
         <v>-31</v>
       </c>
-      <c r="E2" s="32">
+      <c r="E2" s="30">
         <v>24</v>
       </c>
-      <c r="F2" s="32">
+      <c r="F2" s="30">
         <v>196</v>
       </c>
-      <c r="G2" s="32">
+      <c r="G2" s="30">
         <v>344</v>
       </c>
-      <c r="H2" s="32">
+      <c r="H2" s="30">
         <v>329</v>
       </c>
-      <c r="I2" s="32">
+      <c r="I2" s="30">
         <v>328</v>
       </c>
-      <c r="J2" s="32">
+      <c r="J2" s="30">
         <v>313</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="32">
+      <c r="C3" s="30">
         <v>16</v>
       </c>
-      <c r="D3" s="32">
+      <c r="D3" s="30">
         <v>10</v>
       </c>
-      <c r="E3" s="32">
+      <c r="E3" s="30">
         <v>7</v>
       </c>
-      <c r="F3" s="32">
+      <c r="F3" s="30">
         <v>-1</v>
       </c>
-      <c r="G3" s="32">
+      <c r="G3" s="30">
         <v>9</v>
       </c>
-      <c r="H3" s="32">
+      <c r="H3" s="30">
         <v>93</v>
       </c>
-      <c r="I3" s="32">
+      <c r="I3" s="30">
         <v>100</v>
       </c>
-      <c r="J3" s="32">
+      <c r="J3" s="30">
         <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="32">
+      <c r="C4" s="30">
         <v>-46</v>
       </c>
-      <c r="D4" s="32">
+      <c r="D4" s="30">
         <v>79</v>
       </c>
-      <c r="E4" s="32">
+      <c r="E4" s="30">
         <v>195</v>
       </c>
-      <c r="F4" s="32">
+      <c r="F4" s="30">
         <v>226</v>
       </c>
-      <c r="G4" s="32">
+      <c r="G4" s="30">
         <v>190</v>
       </c>
-      <c r="H4" s="32">
+      <c r="H4" s="30">
         <v>137</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="30">
         <v>174</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="30">
         <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="32">
+      <c r="C5" s="30">
         <v>23</v>
       </c>
-      <c r="D5" s="32">
+      <c r="D5" s="30">
         <v>-83</v>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="30">
         <v>-70</v>
       </c>
-      <c r="F5" s="32">
+      <c r="F5" s="30">
         <v>-68</v>
       </c>
-      <c r="G5" s="32">
+      <c r="G5" s="30">
         <v>-91</v>
       </c>
-      <c r="H5" s="32">
+      <c r="H5" s="30">
         <v>-153</v>
       </c>
-      <c r="I5" s="32">
+      <c r="I5" s="30">
         <v>-122</v>
       </c>
-      <c r="J5" s="32">
+      <c r="J5" s="30">
         <v>-98</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="30">
         <v>-98</v>
       </c>
-      <c r="D6" s="32">
+      <c r="D6" s="30">
         <v>-78</v>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="30">
         <v>92</v>
       </c>
-      <c r="F6" s="32">
+      <c r="F6" s="30">
         <v>245</v>
       </c>
-      <c r="G6" s="32">
+      <c r="G6" s="30">
         <v>306</v>
       </c>
-      <c r="H6" s="32">
+      <c r="H6" s="30">
         <v>291</v>
       </c>
-      <c r="I6" s="32">
+      <c r="I6" s="30">
         <v>312</v>
       </c>
-      <c r="J6" s="32">
+      <c r="J6" s="30">
         <v>320</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="30">
         <v>218</v>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="30">
         <v>332</v>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="30">
         <v>186</v>
       </c>
-      <c r="F7" s="32">
+      <c r="F7" s="30">
         <v>146</v>
       </c>
-      <c r="G7" s="32">
+      <c r="G7" s="30">
         <v>236</v>
       </c>
-      <c r="H7" s="32">
+      <c r="H7" s="30">
         <v>272</v>
       </c>
-      <c r="I7" s="32">
+      <c r="I7" s="30">
         <v>421</v>
       </c>
-      <c r="J7" s="32">
+      <c r="J7" s="30">
         <v>480</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="30">
         <v>238</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="30">
         <v>238</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="30">
         <v>238</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="30">
         <v>238</v>
       </c>
-      <c r="G8" s="32">
+      <c r="G8" s="30">
         <v>238</v>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="30">
         <v>198</v>
       </c>
-      <c r="I8" s="32">
+      <c r="I8" s="30">
         <v>198</v>
       </c>
-      <c r="J8" s="32">
+      <c r="J8" s="30">
         <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="30">
         <v>303</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="30">
         <v>467</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="30">
         <v>671</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="30">
         <v>981</v>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="30">
         <v>1230</v>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="30">
         <v>1168</v>
       </c>
-      <c r="I9" s="32">
+      <c r="I9" s="30">
         <v>1411</v>
       </c>
-      <c r="J9" s="32">
+      <c r="J9" s="30">
         <v>1619</v>
       </c>
     </row>
@@ -3971,531 +3979,531 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="31" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="18">
         <v>2039358</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="18">
         <v>2049066</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="18">
         <v>-9708</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="18">
         <v>485782</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="18">
         <v>485394</v>
       </c>
-      <c r="G2" s="20">
+      <c r="G2" s="18">
         <v>388</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="18">
         <v>148470</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="18">
         <v>121000</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="18">
         <v>27470</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="18">
         <v>76003</v>
       </c>
-      <c r="F3" s="20">
+      <c r="F3" s="18">
         <v>60962</v>
       </c>
-      <c r="G3" s="20">
+      <c r="G3" s="18">
         <v>15041</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="18">
         <v>30207</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="18">
         <v>30207</v>
       </c>
-      <c r="D4" s="20">
-        <v>0</v>
-      </c>
-      <c r="E4" s="20">
+      <c r="D4" s="18">
+        <v>0</v>
+      </c>
+      <c r="E4" s="18">
         <v>307</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="18">
         <v>307</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="18">
         <v>585431</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="18">
         <v>515822</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="18">
         <v>69609</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="18">
         <v>23113</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="18">
         <v>13685</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="18">
         <v>9428</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="18">
         <v>2285</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="18">
         <v>2285</v>
       </c>
-      <c r="D6" s="20">
-        <v>0</v>
-      </c>
-      <c r="E6" s="20">
+      <c r="D6" s="18">
+        <v>0</v>
+      </c>
+      <c r="E6" s="18">
         <v>11379</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="18">
         <v>11379</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="18">
         <v>10720</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="18">
         <v>10720</v>
       </c>
-      <c r="D7" s="20">
-        <v>0</v>
-      </c>
-      <c r="E7" s="20">
-        <v>0</v>
-      </c>
-      <c r="F7" s="20">
-        <v>0</v>
-      </c>
-      <c r="G7" s="20">
+      <c r="D7" s="18">
+        <v>0</v>
+      </c>
+      <c r="E7" s="18">
+        <v>0</v>
+      </c>
+      <c r="F7" s="18">
+        <v>0</v>
+      </c>
+      <c r="G7" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="18">
         <v>48884</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="18">
         <v>48331</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="18">
         <v>553</v>
       </c>
-      <c r="E8" s="20">
-        <v>0</v>
-      </c>
-      <c r="F8" s="20">
-        <v>0</v>
-      </c>
-      <c r="G8" s="20">
+      <c r="E8" s="18">
+        <v>0</v>
+      </c>
+      <c r="F8" s="18">
+        <v>0</v>
+      </c>
+      <c r="G8" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="18">
         <v>475751</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="18">
         <v>555751</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="18">
         <v>-80000</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="18">
         <v>44302</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="18">
         <v>44302</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="18">
         <v>1403924</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="18">
         <v>1313451</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="18">
         <v>90473</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="18">
         <v>44160</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="18">
         <v>44160</v>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="18">
         <v>2500</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="18">
         <v>2500</v>
       </c>
-      <c r="D11" s="20">
-        <v>0</v>
-      </c>
-      <c r="E11" s="20">
-        <v>0</v>
-      </c>
-      <c r="F11" s="20">
-        <v>0</v>
-      </c>
-      <c r="G11" s="20">
+      <c r="D11" s="18">
+        <v>0</v>
+      </c>
+      <c r="E11" s="18">
+        <v>0</v>
+      </c>
+      <c r="F11" s="18">
+        <v>0</v>
+      </c>
+      <c r="G11" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="B12" s="20">
-        <v>0</v>
-      </c>
-      <c r="C12" s="20">
-        <v>0</v>
-      </c>
-      <c r="D12" s="20">
-        <v>0</v>
-      </c>
-      <c r="E12" s="20">
+      <c r="B12" s="18">
+        <v>0</v>
+      </c>
+      <c r="C12" s="18">
+        <v>0</v>
+      </c>
+      <c r="D12" s="18">
+        <v>0</v>
+      </c>
+      <c r="E12" s="18">
         <v>11889</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="18">
         <v>11889</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B13" s="18">
         <v>55588</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="18">
         <v>53638</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="18">
         <v>1950</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="18">
         <v>7350</v>
       </c>
-      <c r="F13" s="20">
-        <v>0</v>
-      </c>
-      <c r="G13" s="20">
+      <c r="F13" s="18">
+        <v>0</v>
+      </c>
+      <c r="G13" s="18">
         <v>7350</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="18">
         <v>30821</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="18">
         <v>30821</v>
       </c>
-      <c r="D14" s="20">
-        <v>0</v>
-      </c>
-      <c r="E14" s="20">
+      <c r="D14" s="18">
+        <v>0</v>
+      </c>
+      <c r="E14" s="18">
         <v>190728</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="18">
         <v>190728</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="B15" s="20">
+      <c r="B15" s="18">
         <v>53962</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="18">
         <v>38198</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="18">
         <v>15764</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="18">
         <v>7943</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="18">
         <v>7943</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="18">
         <v>545673</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="18">
         <v>545669</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="18">
         <v>4</v>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="18">
         <v>669047</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="18">
         <v>669720</v>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="18">
         <v>-673</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="B17" s="20">
+      <c r="B17" s="18">
         <v>96589</v>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="18">
         <v>96589</v>
       </c>
-      <c r="D17" s="20">
-        <v>0</v>
-      </c>
-      <c r="E17" s="20">
+      <c r="D17" s="18">
+        <v>0</v>
+      </c>
+      <c r="E17" s="18">
         <v>24323</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="18">
         <v>24323</v>
       </c>
-      <c r="G17" s="20">
+      <c r="G17" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="B18" s="20">
+      <c r="B18" s="18">
         <v>4472</v>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="18">
         <v>4472</v>
       </c>
-      <c r="D18" s="20">
-        <v>0</v>
-      </c>
-      <c r="E18" s="20">
+      <c r="D18" s="18">
+        <v>0</v>
+      </c>
+      <c r="E18" s="18">
         <v>15969</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="18">
         <v>15969</v>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B19" s="20">
+      <c r="B19" s="18">
         <v>1025572</v>
       </c>
-      <c r="C19" s="20">
+      <c r="C19" s="18">
         <v>1025571</v>
       </c>
-      <c r="D19" s="20">
+      <c r="D19" s="18">
         <v>1</v>
       </c>
-      <c r="E19" s="20">
+      <c r="E19" s="18">
         <v>1032250</v>
       </c>
-      <c r="F19" s="20">
+      <c r="F19" s="18">
         <v>1032250</v>
       </c>
-      <c r="G19" s="20">
+      <c r="G19" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B20" s="20">
+      <c r="B20" s="18">
         <v>9112</v>
       </c>
-      <c r="C20" s="20">
+      <c r="C20" s="18">
         <v>12238</v>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="18">
         <v>-3126</v>
       </c>
-      <c r="E20" s="20">
-        <v>0</v>
-      </c>
-      <c r="F20" s="20">
-        <v>0</v>
-      </c>
-      <c r="G20" s="20">
+      <c r="E20" s="18">
+        <v>0</v>
+      </c>
+      <c r="F20" s="18">
+        <v>0</v>
+      </c>
+      <c r="G20" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="20">
+      <c r="B21" s="18">
         <v>6569317</v>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="18">
         <v>6456328</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="18">
         <v>112990</v>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="18">
         <v>2644544</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="18">
         <v>2613011</v>
       </c>
-      <c r="G21" s="20">
+      <c r="G21" s="18">
         <v>31534</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B22" s="20">
+      <c r="B22" s="18">
         <v>7657</v>
       </c>
-      <c r="C22" s="20">
+      <c r="C22" s="18">
         <v>5433</v>
       </c>
-      <c r="D22" s="20">
+      <c r="D22" s="18">
         <v>2224</v>
       </c>
-      <c r="E22" s="20">
-        <v>0</v>
-      </c>
-      <c r="F22" s="20">
-        <v>0</v>
-      </c>
-      <c r="G22" s="20">
+      <c r="E22" s="18">
+        <v>0</v>
+      </c>
+      <c r="F22" s="18">
+        <v>0</v>
+      </c>
+      <c r="G22" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="22">
+      <c r="B23" s="20">
         <v>5960544</v>
       </c>
-      <c r="C23" s="22">
+      <c r="C23" s="20">
         <v>5697855</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="20">
         <v>262689</v>
       </c>
-      <c r="E23" s="22">
+      <c r="E23" s="20">
         <v>2410170</v>
       </c>
-      <c r="F23" s="22">
+      <c r="F23" s="20">
         <v>2366617</v>
       </c>
-      <c r="G23" s="22">
+      <c r="G23" s="20">
         <v>43553</v>
       </c>
     </row>
@@ -4510,84 +4518,84 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="31" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="18">
         <v>3000</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="18">
         <v>17604</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="18">
         <v>2396</v>
       </c>
-      <c r="E2" s="20">
-        <v>0</v>
-      </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
+      <c r="E2" s="18">
+        <v>0</v>
+      </c>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="18">
         <v>4000</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="18">
         <v>1000188</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="18">
         <v>1015205</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="18">
         <v>1341221</v>
       </c>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="22">
+      <c r="B4" s="20">
         <v>7000</v>
       </c>
-      <c r="C4" s="22">
+      <c r="C4" s="20">
         <v>1017791</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="20">
         <v>1017601</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="20">
         <v>1341221</v>
       </c>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4604,837 +4612,837 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="31" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="18">
         <v>135334</v>
       </c>
-      <c r="D2" s="20"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="18">
         <v>659019</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="18">
         <v>28758</v>
       </c>
-      <c r="E3" s="20"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="18">
         <v>2500</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="20">
         <v>796854</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="20">
         <v>28758</v>
       </c>
-      <c r="E5" s="22"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="18">
         <v>140567</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="18">
         <v>7595</v>
       </c>
-      <c r="E6" s="20"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="18">
         <v>462779</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="18">
         <v>2396</v>
       </c>
-      <c r="E7" s="20"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="18">
         <v>9112</v>
       </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="20">
         <v>612459</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="20">
         <v>9991</v>
       </c>
-      <c r="E9" s="22"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="33">
         <v>977135</v>
       </c>
-      <c r="D10" s="35">
+      <c r="D10" s="33">
         <v>340985</v>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="33">
         <v>421696</v>
       </c>
-      <c r="F10" s="35">
+      <c r="F10" s="33">
         <v>199787</v>
       </c>
-      <c r="G10" s="35">
+      <c r="G10" s="33">
         <v>1993</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="18">
         <v>115236</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="18">
         <v>60962</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="18">
         <v>1608</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="18">
         <v>13212</v>
       </c>
-      <c r="G11" s="20"/>
+      <c r="G11" s="18"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="18">
         <v>55588</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="18">
         <v>7350</v>
       </c>
-      <c r="E12" s="20"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="20"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="18"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="20">
         <v>1147959</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="20">
         <v>409297</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="20">
         <v>423304</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="20">
         <v>212999</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="20">
         <v>1993</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="33">
         <v>407703</v>
       </c>
-      <c r="D14" s="35">
+      <c r="D14" s="33">
         <v>2302</v>
       </c>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="36" t="s">
+      <c r="B15" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="35">
         <v>30207</v>
       </c>
-      <c r="D15" s="37">
+      <c r="D15" s="35">
         <v>307</v>
       </c>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="18">
         <v>2285</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="18">
         <v>11379</v>
       </c>
-      <c r="E16" s="20"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="18">
         <v>10720</v>
       </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="18">
         <v>48884</v>
       </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="20">
+      <c r="C19" s="18">
         <v>84417</v>
       </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="20">
+      <c r="C20" s="18">
         <v>14714</v>
       </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="18">
         <v>53962</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="18">
         <v>7943</v>
       </c>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="20">
+      <c r="C22" s="18">
         <v>168263</v>
       </c>
-      <c r="D22" s="20">
+      <c r="D22" s="18">
         <v>147858</v>
       </c>
-      <c r="E22" s="20">
+      <c r="E22" s="18">
         <v>3071</v>
       </c>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C23" s="20">
+      <c r="C23" s="18">
         <v>96589</v>
       </c>
-      <c r="D23" s="20">
+      <c r="D23" s="18">
         <v>24323</v>
       </c>
-      <c r="E23" s="19"/>
-      <c r="F23" s="20">
+      <c r="E23" s="17"/>
+      <c r="F23" s="18">
         <v>2002</v>
       </c>
-      <c r="G23" s="19"/>
+      <c r="G23" s="17"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="20">
+      <c r="C24" s="18">
         <v>4472</v>
       </c>
-      <c r="D24" s="20">
+      <c r="D24" s="18">
         <v>15969</v>
       </c>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="19"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="17"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="20">
+      <c r="C25" s="18">
         <v>4295</v>
       </c>
-      <c r="D25" s="20">
+      <c r="D25" s="18">
         <v>14703</v>
       </c>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="19"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="17"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C26" s="22">
+      <c r="C26" s="20">
         <v>926510</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="20">
         <v>224784</v>
       </c>
-      <c r="E26" s="22">
+      <c r="E26" s="20">
         <v>3071</v>
       </c>
-      <c r="F26" s="22">
+      <c r="F26" s="20">
         <v>2002</v>
       </c>
-      <c r="G26" s="18"/>
+      <c r="G26" s="16"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="19" t="s">
+      <c r="A27" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="20">
+      <c r="C27" s="18">
         <v>328272</v>
       </c>
-      <c r="D27" s="20">
+      <c r="D27" s="18">
         <v>46710</v>
       </c>
-      <c r="E27" s="20">
+      <c r="E27" s="18">
         <v>14980</v>
       </c>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="38" t="s">
+      <c r="A28" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="C28" s="39">
+      <c r="C28" s="37">
         <v>33234</v>
       </c>
-      <c r="D28" s="39">
+      <c r="D28" s="37">
         <v>15041</v>
       </c>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="38"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="36"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="34" t="s">
+      <c r="A29" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B29" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="C29" s="35">
+      <c r="C29" s="33">
         <v>309529</v>
       </c>
-      <c r="D29" s="35">
+      <c r="D29" s="33">
         <v>15518</v>
       </c>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="34"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="32"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="36" t="s">
+      <c r="A30" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="36" t="s">
+      <c r="B30" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="37">
+      <c r="C30" s="35">
         <v>391334</v>
       </c>
-      <c r="D30" s="37">
+      <c r="D30" s="35">
         <v>44302</v>
       </c>
-      <c r="E30" s="37"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="36"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="34"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
+      <c r="A31" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="20">
+      <c r="C31" s="18">
         <v>267411</v>
       </c>
-      <c r="D31" s="20">
+      <c r="D31" s="18">
         <v>13006</v>
       </c>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="19"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="17"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
+      <c r="A32" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20">
+      <c r="C32" s="18"/>
+      <c r="D32" s="18">
         <v>11889</v>
       </c>
-      <c r="E32" s="20">
+      <c r="E32" s="18">
         <v>13223</v>
       </c>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
+      <c r="A33" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B33" s="19" t="s">
+      <c r="B33" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="C33" s="20">
+      <c r="C33" s="18">
         <v>30821</v>
       </c>
-      <c r="D33" s="20">
+      <c r="D33" s="18">
         <v>190728</v>
       </c>
-      <c r="E33" s="20"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="19" t="s">
+      <c r="A34" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="C34" s="20">
+      <c r="C34" s="18">
         <v>310398</v>
       </c>
-      <c r="D34" s="20">
+      <c r="D34" s="18">
         <v>239120</v>
       </c>
-      <c r="E34" s="20">
+      <c r="E34" s="18">
         <v>5790</v>
       </c>
-      <c r="F34" s="20">
+      <c r="F34" s="18">
         <v>5710</v>
       </c>
-      <c r="G34" s="19"/>
+      <c r="G34" s="17"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="B35" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="22">
+      <c r="C35" s="20">
         <v>1670999</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="20">
         <v>576313</v>
       </c>
-      <c r="E35" s="22">
+      <c r="E35" s="20">
         <v>33993</v>
       </c>
-      <c r="F35" s="22">
+      <c r="F35" s="20">
         <v>5710</v>
       </c>
-      <c r="G35" s="18"/>
+      <c r="G35" s="16"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
+      <c r="A36" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="C36" s="20">
+      <c r="C36" s="18">
         <v>326249</v>
       </c>
-      <c r="D36" s="20">
+      <c r="D36" s="18">
         <v>95785</v>
       </c>
-      <c r="E36" s="20"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="20"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="18"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="38" t="s">
+      <c r="A37" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="B37" s="38" t="s">
+      <c r="B37" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="C37" s="39">
+      <c r="C37" s="37">
         <v>67011</v>
       </c>
-      <c r="D37" s="39">
+      <c r="D37" s="37">
         <v>282069</v>
       </c>
-      <c r="E37" s="39">
+      <c r="E37" s="37">
         <v>6655</v>
       </c>
-      <c r="F37" s="39"/>
-      <c r="G37" s="39"/>
+      <c r="F37" s="37"/>
+      <c r="G37" s="37"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="34" t="s">
+      <c r="A38" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="B38" s="34" t="s">
+      <c r="B38" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="C38" s="35">
+      <c r="C38" s="33">
         <v>1021277</v>
       </c>
-      <c r="D38" s="35">
+      <c r="D38" s="33">
         <v>1017547</v>
       </c>
-      <c r="E38" s="35">
+      <c r="E38" s="33">
         <v>1341221</v>
       </c>
-      <c r="F38" s="35">
+      <c r="F38" s="33">
         <v>78387</v>
       </c>
-      <c r="G38" s="35"/>
+      <c r="G38" s="33"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="18" t="s">
+      <c r="A39" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B39" s="18" t="s">
+      <c r="B39" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C39" s="22">
+      <c r="C39" s="20">
         <v>1414537</v>
       </c>
-      <c r="D39" s="22">
+      <c r="D39" s="20">
         <v>1395400</v>
       </c>
-      <c r="E39" s="22">
+      <c r="E39" s="20">
         <v>1347876</v>
       </c>
-      <c r="F39" s="22">
+      <c r="F39" s="20">
         <v>78387</v>
       </c>
-      <c r="G39" s="22"/>
+      <c r="G39" s="20"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="18" t="s">
+      <c r="A40" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B40" s="18" t="s">
+      <c r="B40" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C40" s="22">
+      <c r="C40" s="20">
         <v>6569317</v>
       </c>
-      <c r="D40" s="22">
+      <c r="D40" s="20">
         <v>2644544</v>
       </c>
-      <c r="E40" s="22">
+      <c r="E40" s="20">
         <v>1808244</v>
       </c>
-      <c r="F40" s="22">
+      <c r="F40" s="20">
         <v>299098</v>
       </c>
-      <c r="G40" s="22">
+      <c r="G40" s="20">
         <v>1993</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="19" t="s">
+      <c r="A41" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B41" s="19" t="s">
+      <c r="B41" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="20">
+      <c r="C41" s="18">
         <v>127113</v>
       </c>
-      <c r="D41" s="20">
+      <c r="D41" s="18">
         <v>67011</v>
       </c>
-      <c r="E41" s="20">
+      <c r="E41" s="18">
         <v>282069</v>
       </c>
-      <c r="F41" s="20">
+      <c r="F41" s="18">
         <v>6655</v>
       </c>
-      <c r="G41" s="20"/>
+      <c r="G41" s="18"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="38" t="s">
+      <c r="A42" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="B42" s="38" t="s">
+      <c r="B42" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="C42" s="39">
+      <c r="C42" s="37">
         <v>1257909</v>
       </c>
-      <c r="D42" s="39">
+      <c r="D42" s="37">
         <v>1021276</v>
       </c>
-      <c r="E42" s="39">
+      <c r="E42" s="37">
         <v>1017547</v>
       </c>
-      <c r="F42" s="39">
+      <c r="F42" s="37">
         <v>1341221</v>
       </c>
-      <c r="G42" s="39">
+      <c r="G42" s="37">
         <v>78387</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="18" t="s">
+      <c r="A43" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B43" s="18" t="s">
+      <c r="B43" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="22">
+      <c r="C43" s="20">
         <v>2104430</v>
       </c>
-      <c r="D43" s="22">
+      <c r="D43" s="20">
         <v>1414531</v>
       </c>
-      <c r="E43" s="22">
+      <c r="E43" s="20">
         <v>1395862</v>
       </c>
-      <c r="F43" s="22">
+      <c r="F43" s="20">
         <v>1347876</v>
       </c>
-      <c r="G43" s="22">
+      <c r="G43" s="20">
         <v>78387</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="18" t="s">
+      <c r="A44" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B44" s="18" t="s">
+      <c r="B44" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C44" s="22">
+      <c r="C44" s="20">
         <v>15494303</v>
       </c>
-      <c r="D44" s="22">
+      <c r="D44" s="20">
         <v>5697855</v>
       </c>
-      <c r="E44" s="22">
+      <c r="E44" s="20">
         <v>2366617</v>
       </c>
-      <c r="F44" s="22">
+      <c r="F44" s="20">
         <v>1658881</v>
       </c>
-      <c r="G44" s="22">
+      <c r="G44" s="20">
         <v>275192</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="18" t="s">
+      <c r="A45" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B45" s="18" t="s">
+      <c r="B45" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="22">
+      <c r="C45" s="20">
         <v>13167328</v>
       </c>
-      <c r="D45" s="22">
+      <c r="D45" s="20">
         <v>4686629</v>
       </c>
-      <c r="E45" s="22">
+      <c r="E45" s="20">
         <v>2311588</v>
       </c>
-      <c r="F45" s="22">
+      <c r="F45" s="20">
         <v>1610210</v>
       </c>
-      <c r="G45" s="22">
+      <c r="G45" s="20">
         <v>247668</v>
       </c>
     </row>
@@ -5457,186 +5465,186 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="31" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="18">
         <v>743183</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="18">
         <v>796854</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="18">
         <v>28758</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="18">
         <v>28758</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="18">
         <v>53671</v>
       </c>
-      <c r="G2" s="20">
+      <c r="G2" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="18">
         <v>575509</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="18">
         <v>612459</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="18">
         <v>9991</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="18">
         <v>9991</v>
       </c>
-      <c r="F3" s="20">
+      <c r="F3" s="18">
         <v>36950</v>
       </c>
-      <c r="G3" s="20">
+      <c r="G3" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="18">
         <v>1147811</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="18">
         <v>1147959</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="18">
         <v>401098</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="18">
         <v>409297</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="18">
         <v>148</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="18">
         <v>8199</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="18">
         <v>910090</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="18">
         <v>926510</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="18">
         <v>224784</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="18">
         <v>224784</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="18">
         <v>16420</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="18">
         <v>1665200</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="18">
         <v>1670999</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="18">
         <v>552518</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="18">
         <v>576313</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="18">
         <v>5799</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="18">
         <v>23795</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="18">
         <v>1414534</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="18">
         <v>1414537</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="18">
         <v>1395862</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="18">
         <v>1395400</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="18">
         <v>3</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="24">
         <v>-462</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="18">
         <v>6456328</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="18">
         <v>6569317</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="18">
         <v>2613011</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="18">
         <v>2644544</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="18">
         <v>112989</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="18">
         <v>31533</v>
       </c>
     </row>

--- a/template.xlsx
+++ b/template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\1. Work\1. Daily\Capacity Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686AACC4-307D-459E-A2CD-42A595D57FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC010E3F-0483-411F-84C9-BA16D1E5C277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="810" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -396,10 +396,10 @@
     <t>Available Capacity (First)</t>
   </si>
   <si>
-    <t>July</t>
-  </si>
-  <si>
     <t>August</t>
+  </si>
+  <si>
+    <t>September</t>
   </si>
 </sst>
 </file>
@@ -409,7 +409,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -483,18 +483,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -693,7 +681,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -761,11 +749,14 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="4" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -774,7 +765,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -782,12 +772,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="4" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1109,18 +1093,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
+      <c r="A1" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
       <c r="K1" s="5"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1154,18 +1138,18 @@
       <c r="B3" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="59" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="55"/>
       <c r="G3" s="61" t="s">
         <v>119</v>
       </c>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="55"/>
       <c r="K3" s="5"/>
       <c r="L3" s="16" t="s">
         <v>5</v>
@@ -1194,11 +1178,11 @@
       <c r="B4" s="63"/>
       <c r="C4" s="48">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46230</v>
       </c>
       <c r="D4" s="48">
         <f ca="1">C4-1</f>
-        <v>46203</v>
+        <v>46229</v>
       </c>
       <c r="E4" s="49" t="s">
         <v>12</v>
@@ -1208,11 +1192,11 @@
       </c>
       <c r="G4" s="48">
         <f ca="1">C4</f>
-        <v>46204</v>
+        <v>46230</v>
       </c>
       <c r="H4" s="48">
         <f ca="1">D4</f>
-        <v>46203</v>
+        <v>46229</v>
       </c>
       <c r="I4" s="49" t="s">
         <v>12</v>
@@ -1242,31 +1226,31 @@
       <c r="B5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="53">
-        <v>-586</v>
-      </c>
-      <c r="D5" s="53">
-        <v>-539</v>
-      </c>
-      <c r="E5" s="53">
-        <v>47</v>
-      </c>
-      <c r="F5" s="51">
+      <c r="C5" s="24">
+        <v>-64</v>
+      </c>
+      <c r="D5" s="24">
+        <v>-60</v>
+      </c>
+      <c r="E5" s="51">
+        <v>4</v>
+      </c>
+      <c r="F5" s="53">
         <f>C5/C60</f>
-        <v>-0.33639494833524686</v>
-      </c>
-      <c r="G5" s="66">
-        <v>1214</v>
-      </c>
-      <c r="H5" s="66">
-        <v>1378</v>
-      </c>
-      <c r="I5" s="66">
-        <v>164</v>
+        <v>-3.8208955223880597E-2</v>
+      </c>
+      <c r="G5" s="51">
+        <v>1402</v>
+      </c>
+      <c r="H5" s="51">
+        <v>1429</v>
+      </c>
+      <c r="I5" s="51">
+        <v>27</v>
       </c>
       <c r="J5" s="7">
         <f>G5/D60</f>
-        <v>0.72477611940298503</v>
+        <v>0.80482204362801379</v>
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="17" t="s">
@@ -1292,31 +1276,31 @@
       <c r="B6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="53">
-        <v>-227</v>
-      </c>
-      <c r="D6" s="53">
-        <v>-105</v>
-      </c>
-      <c r="E6" s="54">
-        <v>122</v>
-      </c>
-      <c r="F6" s="51">
+      <c r="C6" s="51">
+        <v>164</v>
+      </c>
+      <c r="D6" s="51">
+        <v>198</v>
+      </c>
+      <c r="E6" s="51">
+        <v>34</v>
+      </c>
+      <c r="F6" s="7">
         <f t="shared" ref="F6:F11" si="0">C6/C61</f>
-        <v>-0.28719635627530365</v>
-      </c>
-      <c r="G6" s="66">
-        <v>199</v>
-      </c>
-      <c r="H6" s="66">
-        <v>278</v>
-      </c>
-      <c r="I6" s="66">
-        <v>79</v>
+        <v>0.21578947368421053</v>
+      </c>
+      <c r="G6" s="51">
+        <v>430</v>
+      </c>
+      <c r="H6" s="51">
+        <v>438</v>
+      </c>
+      <c r="I6" s="51">
+        <v>8</v>
       </c>
       <c r="J6" s="7">
         <f t="shared" ref="J6:J12" si="1">G6/D61</f>
-        <v>0.26184210526315788</v>
+        <v>0.54402834008097167</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="17" t="s">
@@ -1340,31 +1324,31 @@
       <c r="B7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="53">
-        <v>-140</v>
-      </c>
-      <c r="D7" s="53">
-        <v>-40</v>
-      </c>
-      <c r="E7" s="53">
-        <v>100</v>
-      </c>
-      <c r="F7" s="51">
+      <c r="C7" s="51">
+        <v>462</v>
+      </c>
+      <c r="D7" s="51">
+        <v>485</v>
+      </c>
+      <c r="E7" s="51">
+        <v>23</v>
+      </c>
+      <c r="F7" s="7">
         <f t="shared" si="0"/>
-        <v>-7.0803621099479089E-2</v>
-      </c>
-      <c r="G7" s="66">
-        <v>1132</v>
-      </c>
-      <c r="H7" s="66">
-        <v>1287</v>
-      </c>
-      <c r="I7" s="66">
-        <v>155</v>
+        <v>0.24299802761341222</v>
+      </c>
+      <c r="G7" s="51">
+        <v>771</v>
+      </c>
+      <c r="H7" s="51">
+        <v>990</v>
+      </c>
+      <c r="I7" s="51">
+        <v>219</v>
       </c>
       <c r="J7" s="7">
         <f t="shared" si="1"/>
-        <v>0.59539776462853389</v>
+        <v>0.38992565619784558</v>
       </c>
       <c r="K7" s="5"/>
       <c r="L7" s="16" t="s">
@@ -1390,31 +1374,31 @@
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="54">
-        <v>-33</v>
-      </c>
-      <c r="D8" s="53">
-        <v>1</v>
-      </c>
-      <c r="E8" s="53">
-        <v>34</v>
-      </c>
-      <c r="F8" s="51">
+      <c r="C8" s="51">
+        <v>18</v>
+      </c>
+      <c r="D8" s="51">
+        <v>53</v>
+      </c>
+      <c r="E8" s="51">
+        <v>35</v>
+      </c>
+      <c r="F8" s="7">
         <f t="shared" si="0"/>
-        <v>-2.0275251904644874E-2</v>
-      </c>
-      <c r="G8" s="24">
-        <v>-149</v>
-      </c>
-      <c r="H8" s="24">
-        <v>-12</v>
-      </c>
-      <c r="I8" s="66">
-        <v>137</v>
-      </c>
-      <c r="J8" s="51">
+        <v>1.1501597444089457E-2</v>
+      </c>
+      <c r="G8" s="51">
+        <v>28</v>
+      </c>
+      <c r="H8" s="51">
+        <v>77</v>
+      </c>
+      <c r="I8" s="51">
+        <v>49</v>
+      </c>
+      <c r="J8" s="7">
         <f t="shared" si="1"/>
-        <v>-9.5207667731629392E-2</v>
+        <v>1.7203244040304745E-2</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="17" t="s">
@@ -1440,31 +1424,31 @@
       <c r="B9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="53">
-        <v>-228</v>
-      </c>
-      <c r="D9" s="53">
-        <v>-305</v>
-      </c>
-      <c r="E9" s="54">
-        <v>-77</v>
-      </c>
-      <c r="F9" s="51">
+      <c r="C9" s="51">
+        <v>305</v>
+      </c>
+      <c r="D9" s="51">
+        <v>435</v>
+      </c>
+      <c r="E9" s="51">
+        <v>130</v>
+      </c>
+      <c r="F9" s="7">
         <f t="shared" si="0"/>
-        <v>-0.1449459631277813</v>
-      </c>
-      <c r="G9" s="66">
-        <v>920</v>
-      </c>
-      <c r="H9" s="66">
-        <v>984</v>
-      </c>
-      <c r="I9" s="66">
-        <v>64</v>
+        <v>0.20165289256198346</v>
+      </c>
+      <c r="G9" s="51">
+        <v>1508</v>
+      </c>
+      <c r="H9" s="51">
+        <v>1482</v>
+      </c>
+      <c r="I9" s="24">
+        <v>-26</v>
       </c>
       <c r="J9" s="7">
         <f t="shared" si="1"/>
-        <v>0.60826446280991731</v>
+        <v>0.95867768595041325</v>
       </c>
       <c r="K9" s="5"/>
       <c r="L9" s="17" t="s">
@@ -1490,31 +1474,31 @@
       <c r="B10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="53">
-        <v>-1001</v>
-      </c>
-      <c r="D10" s="53">
-        <v>-425</v>
-      </c>
-      <c r="E10" s="54">
-        <v>576</v>
-      </c>
-      <c r="F10" s="51">
+      <c r="C10" s="51">
+        <v>533</v>
+      </c>
+      <c r="D10" s="51">
+        <v>633</v>
+      </c>
+      <c r="E10" s="51">
+        <v>100</v>
+      </c>
+      <c r="F10" s="7">
         <f t="shared" si="0"/>
-        <v>-0.35648148148148145</v>
-      </c>
-      <c r="G10" s="66">
-        <v>2058</v>
-      </c>
-      <c r="H10" s="66">
-        <v>2261</v>
-      </c>
-      <c r="I10" s="66">
-        <v>203</v>
+        <v>0.19740740740740742</v>
+      </c>
+      <c r="G10" s="51">
+        <v>1824</v>
+      </c>
+      <c r="H10" s="51">
+        <v>1880</v>
+      </c>
+      <c r="I10" s="51">
+        <v>56</v>
       </c>
       <c r="J10" s="7">
         <f t="shared" si="1"/>
-        <v>0.76222222222222225</v>
+        <v>0.6495726495726496</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="17" t="s">
@@ -1538,31 +1522,31 @@
       <c r="B11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="53">
-        <v>-112</v>
-      </c>
-      <c r="D11" s="53">
-        <v>-82</v>
-      </c>
-      <c r="E11" s="53">
-        <v>30</v>
-      </c>
-      <c r="F11" s="51">
+      <c r="C11" s="51">
+        <v>317</v>
+      </c>
+      <c r="D11" s="51">
+        <v>423</v>
+      </c>
+      <c r="E11" s="51">
+        <v>106</v>
+      </c>
+      <c r="F11" s="7">
         <f t="shared" si="0"/>
-        <v>-0.10878010878010877</v>
-      </c>
-      <c r="G11" s="66">
-        <v>674</v>
-      </c>
-      <c r="H11" s="66">
-        <v>624</v>
-      </c>
-      <c r="I11" s="24">
-        <v>-50</v>
+        <v>0.32020202020202021</v>
+      </c>
+      <c r="G11" s="51">
+        <v>975</v>
+      </c>
+      <c r="H11" s="51">
+        <v>982</v>
+      </c>
+      <c r="I11" s="51">
+        <v>7</v>
       </c>
       <c r="J11" s="7">
         <f t="shared" si="1"/>
-        <v>0.68080808080808086</v>
+        <v>0.94696969696969702</v>
       </c>
       <c r="K11" s="5"/>
       <c r="L11" s="16" t="s">
@@ -1588,31 +1572,31 @@
       <c r="B12" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="55">
-        <v>-2328</v>
-      </c>
-      <c r="D12" s="55">
-        <v>-1494</v>
-      </c>
-      <c r="E12" s="55">
-        <v>834</v>
-      </c>
-      <c r="F12" s="52">
+      <c r="C12" s="52">
+        <v>1734</v>
+      </c>
+      <c r="D12" s="52">
+        <v>2167</v>
+      </c>
+      <c r="E12" s="52">
+        <v>433</v>
+      </c>
+      <c r="F12" s="50">
         <f>C12/C67</f>
-        <v>-0.20159509521211649</v>
-      </c>
-      <c r="G12" s="67">
-        <v>6049</v>
-      </c>
-      <c r="H12" s="67">
-        <v>6800</v>
-      </c>
-      <c r="I12" s="67">
-        <v>751</v>
+        <v>0.15616345829111786</v>
+      </c>
+      <c r="G12" s="52">
+        <v>6938</v>
+      </c>
+      <c r="H12" s="52">
+        <v>7279</v>
+      </c>
+      <c r="I12" s="52">
+        <v>341</v>
       </c>
       <c r="J12" s="50">
         <f t="shared" si="1"/>
-        <v>0.54477091072835748</v>
+        <v>0.60080187739762214</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="17" t="s">
@@ -1638,24 +1622,24 @@
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="64"/>
-      <c r="B13" s="60"/>
-      <c r="C13" s="65" t="s">
+      <c r="A13" s="54"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="65">
+      <c r="D13" s="55"/>
+      <c r="E13" s="56">
+        <v>25</v>
+      </c>
+      <c r="F13" s="55"/>
+      <c r="G13" s="56" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="55"/>
+      <c r="I13" s="56">
         <v>26</v>
       </c>
-      <c r="F13" s="60"/>
-      <c r="G13" s="65" t="s">
-        <v>29</v>
-      </c>
-      <c r="H13" s="60"/>
-      <c r="I13" s="65">
-        <v>25</v>
-      </c>
-      <c r="J13" s="60"/>
+      <c r="J13" s="55"/>
       <c r="K13" s="5"/>
       <c r="L13" s="17" t="s">
         <v>19</v>
@@ -3169,11 +3153,11 @@
       </c>
       <c r="C60" s="5">
         <f>(B60/20)*$E$13</f>
-        <v>1742</v>
+        <v>1675</v>
       </c>
       <c r="D60" s="5">
         <f t="shared" ref="D60:D67" si="2">B60*$I$13/20</f>
-        <v>1675</v>
+        <v>1742</v>
       </c>
       <c r="L60" s="25"/>
       <c r="M60" s="25"/>
@@ -3192,11 +3176,11 @@
       </c>
       <c r="C61" s="5">
         <f t="shared" ref="C61:C67" si="3">(B61/20)*$E$13</f>
-        <v>790.4</v>
+        <v>760</v>
       </c>
       <c r="D61" s="5">
         <f t="shared" si="2"/>
-        <v>760</v>
+        <v>790.4</v>
       </c>
       <c r="L61" s="25"/>
       <c r="M61" s="25"/>
@@ -3215,11 +3199,11 @@
       </c>
       <c r="C62" s="5">
         <f t="shared" si="3"/>
-        <v>1977.3</v>
+        <v>1901.25</v>
       </c>
       <c r="D62" s="5">
         <f t="shared" si="2"/>
-        <v>1901.25</v>
+        <v>1977.3</v>
       </c>
       <c r="L62" s="25"/>
       <c r="M62" s="25"/>
@@ -3238,11 +3222,11 @@
       </c>
       <c r="C63" s="5">
         <f t="shared" si="3"/>
-        <v>1627.6000000000001</v>
+        <v>1565</v>
       </c>
       <c r="D63" s="5">
         <f t="shared" si="2"/>
-        <v>1565</v>
+        <v>1627.6</v>
       </c>
       <c r="L63" s="25"/>
       <c r="M63" s="25"/>
@@ -3261,11 +3245,11 @@
       </c>
       <c r="C64" s="5">
         <f t="shared" si="3"/>
-        <v>1573</v>
+        <v>1512.5</v>
       </c>
       <c r="D64" s="5">
         <f t="shared" si="2"/>
-        <v>1512.5</v>
+        <v>1573</v>
       </c>
       <c r="L64" s="25"/>
       <c r="M64" s="25"/>
@@ -3284,11 +3268,11 @@
       </c>
       <c r="C65" s="5">
         <f t="shared" si="3"/>
-        <v>2808</v>
+        <v>2700</v>
       </c>
       <c r="D65" s="5">
         <f t="shared" si="2"/>
-        <v>2700</v>
+        <v>2808</v>
       </c>
       <c r="L65" s="25"/>
       <c r="M65" s="25"/>
@@ -3307,11 +3291,11 @@
       </c>
       <c r="C66" s="5">
         <f t="shared" si="3"/>
-        <v>1029.6000000000001</v>
+        <v>990</v>
       </c>
       <c r="D66" s="5">
         <f t="shared" si="2"/>
-        <v>990</v>
+        <v>1029.5999999999999</v>
       </c>
       <c r="L66" s="25"/>
       <c r="M66" s="25"/>
@@ -3330,11 +3314,11 @@
       </c>
       <c r="C67" s="5">
         <f t="shared" si="3"/>
-        <v>11547.9</v>
+        <v>11103.75</v>
       </c>
       <c r="D67" s="5">
         <f t="shared" si="2"/>
-        <v>11103.75</v>
+        <v>11547.9</v>
       </c>
       <c r="L67" s="25"/>
       <c r="M67" s="25"/>
@@ -3393,16 +3377,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A3:A4"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="G13:H13"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A3:A4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="51" fitToHeight="0" orientation="landscape" r:id="rId1"/>

--- a/template.xlsx
+++ b/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\1. Work\1. Daily\Capacity Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC010E3F-0483-411F-84C9-BA16D1E5C277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166C5124-C16E-4E02-99CA-0B0B7628DF51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="810" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -409,7 +409,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -485,6 +485,21 @@
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="10">
@@ -681,7 +696,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -749,8 +764,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="4" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -772,6 +785,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="15" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1093,18 +1111,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="57" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
+      <c r="A1" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
       <c r="K1" s="5"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1132,24 +1150,24 @@
       <c r="R2" s="15"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="59" t="s">
+      <c r="C3" s="57" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="61" t="s">
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="59" t="s">
         <v>119</v>
       </c>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="55"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="53"/>
       <c r="K3" s="5"/>
       <c r="L3" s="16" t="s">
         <v>5</v>
@@ -1174,15 +1192,15 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="63"/>
-      <c r="B4" s="63"/>
+      <c r="A4" s="61"/>
+      <c r="B4" s="61"/>
       <c r="C4" s="48">
         <f ca="1">TODAY()</f>
-        <v>46230</v>
+        <v>46235</v>
       </c>
       <c r="D4" s="48">
         <f ca="1">C4-1</f>
-        <v>46229</v>
+        <v>46234</v>
       </c>
       <c r="E4" s="49" t="s">
         <v>12</v>
@@ -1192,11 +1210,11 @@
       </c>
       <c r="G4" s="48">
         <f ca="1">C4</f>
-        <v>46230</v>
+        <v>46235</v>
       </c>
       <c r="H4" s="48">
         <f ca="1">D4</f>
-        <v>46229</v>
+        <v>46234</v>
       </c>
       <c r="I4" s="49" t="s">
         <v>12</v>
@@ -1226,31 +1244,31 @@
       <c r="B5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="24">
-        <v>-64</v>
-      </c>
-      <c r="D5" s="24">
-        <v>-60</v>
-      </c>
-      <c r="E5" s="51">
-        <v>4</v>
-      </c>
-      <c r="F5" s="53">
+      <c r="C5" s="62">
+        <v>-25</v>
+      </c>
+      <c r="D5" s="62">
+        <v>-63</v>
+      </c>
+      <c r="E5" s="62">
+        <v>-38</v>
+      </c>
+      <c r="F5" s="51">
         <f>C5/C60</f>
-        <v>-3.8208955223880597E-2</v>
-      </c>
-      <c r="G5" s="51">
-        <v>1402</v>
-      </c>
-      <c r="H5" s="51">
-        <v>1429</v>
-      </c>
-      <c r="I5" s="51">
-        <v>27</v>
+        <v>-1.4925373134328358E-2</v>
+      </c>
+      <c r="G5" s="63">
+        <v>1311</v>
+      </c>
+      <c r="H5" s="63">
+        <v>1409</v>
+      </c>
+      <c r="I5" s="63">
+        <v>98</v>
       </c>
       <c r="J5" s="7">
         <f>G5/D60</f>
-        <v>0.80482204362801379</v>
+        <v>0.7525832376578645</v>
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="17" t="s">
@@ -1276,31 +1294,31 @@
       <c r="B6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="51">
-        <v>164</v>
-      </c>
-      <c r="D6" s="51">
-        <v>198</v>
-      </c>
-      <c r="E6" s="51">
-        <v>34</v>
-      </c>
-      <c r="F6" s="7">
+      <c r="C6" s="62">
+        <v>-16</v>
+      </c>
+      <c r="D6" s="63">
+        <v>129</v>
+      </c>
+      <c r="E6" s="63">
+        <v>145</v>
+      </c>
+      <c r="F6" s="51">
         <f t="shared" ref="F6:F11" si="0">C6/C61</f>
-        <v>0.21578947368421053</v>
-      </c>
-      <c r="G6" s="51">
-        <v>430</v>
-      </c>
-      <c r="H6" s="51">
-        <v>438</v>
-      </c>
-      <c r="I6" s="51">
-        <v>8</v>
+        <v>-2.1052631578947368E-2</v>
+      </c>
+      <c r="G6" s="63">
+        <v>396</v>
+      </c>
+      <c r="H6" s="63">
+        <v>426</v>
+      </c>
+      <c r="I6" s="63">
+        <v>30</v>
       </c>
       <c r="J6" s="7">
         <f t="shared" ref="J6:J12" si="1">G6/D61</f>
-        <v>0.54402834008097167</v>
+        <v>0.50101214574898789</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="17" t="s">
@@ -1324,31 +1342,31 @@
       <c r="B7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="51">
-        <v>462</v>
-      </c>
-      <c r="D7" s="51">
-        <v>485</v>
-      </c>
-      <c r="E7" s="51">
-        <v>23</v>
-      </c>
-      <c r="F7" s="7">
+      <c r="C7" s="62">
+        <v>-194</v>
+      </c>
+      <c r="D7" s="63">
+        <v>412</v>
+      </c>
+      <c r="E7" s="63">
+        <v>606</v>
+      </c>
+      <c r="F7" s="51">
         <f t="shared" si="0"/>
-        <v>0.24299802761341222</v>
-      </c>
-      <c r="G7" s="51">
-        <v>771</v>
-      </c>
-      <c r="H7" s="51">
-        <v>990</v>
-      </c>
-      <c r="I7" s="51">
-        <v>219</v>
+        <v>-0.10203813280736358</v>
+      </c>
+      <c r="G7" s="63">
+        <v>727</v>
+      </c>
+      <c r="H7" s="63">
+        <v>782</v>
+      </c>
+      <c r="I7" s="63">
+        <v>55</v>
       </c>
       <c r="J7" s="7">
         <f t="shared" si="1"/>
-        <v>0.38992565619784558</v>
+        <v>0.36767308956658068</v>
       </c>
       <c r="K7" s="5"/>
       <c r="L7" s="16" t="s">
@@ -1374,31 +1392,31 @@
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="51">
-        <v>18</v>
-      </c>
-      <c r="D8" s="51">
-        <v>53</v>
-      </c>
-      <c r="E8" s="51">
-        <v>35</v>
-      </c>
-      <c r="F8" s="7">
+      <c r="C8" s="62">
+        <v>-62</v>
+      </c>
+      <c r="D8" s="62">
+        <v>-31</v>
+      </c>
+      <c r="E8" s="63">
+        <v>31</v>
+      </c>
+      <c r="F8" s="51">
         <f t="shared" si="0"/>
-        <v>1.1501597444089457E-2</v>
-      </c>
-      <c r="G8" s="51">
-        <v>28</v>
-      </c>
-      <c r="H8" s="51">
-        <v>77</v>
-      </c>
-      <c r="I8" s="51">
-        <v>49</v>
-      </c>
-      <c r="J8" s="7">
+        <v>-3.9616613418530351E-2</v>
+      </c>
+      <c r="G8" s="62">
+        <v>-117</v>
+      </c>
+      <c r="H8" s="62">
+        <v>-100</v>
+      </c>
+      <c r="I8" s="63">
+        <v>17</v>
+      </c>
+      <c r="J8" s="51">
         <f t="shared" si="1"/>
-        <v>1.7203244040304745E-2</v>
+        <v>-7.1884984025559109E-2</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="17" t="s">
@@ -1424,31 +1442,31 @@
       <c r="B9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="51">
-        <v>305</v>
-      </c>
-      <c r="D9" s="51">
-        <v>435</v>
-      </c>
-      <c r="E9" s="51">
-        <v>130</v>
+      <c r="C9" s="63">
+        <v>89</v>
+      </c>
+      <c r="D9" s="63">
+        <v>236</v>
+      </c>
+      <c r="E9" s="63">
+        <v>147</v>
       </c>
       <c r="F9" s="7">
         <f t="shared" si="0"/>
-        <v>0.20165289256198346</v>
-      </c>
-      <c r="G9" s="51">
-        <v>1508</v>
-      </c>
-      <c r="H9" s="51">
-        <v>1482</v>
-      </c>
-      <c r="I9" s="24">
-        <v>-26</v>
+        <v>5.8842975206611567E-2</v>
+      </c>
+      <c r="G9" s="63">
+        <v>1176</v>
+      </c>
+      <c r="H9" s="63">
+        <v>1358</v>
+      </c>
+      <c r="I9" s="63">
+        <v>182</v>
       </c>
       <c r="J9" s="7">
         <f t="shared" si="1"/>
-        <v>0.95867768595041325</v>
+        <v>0.74761602034329311</v>
       </c>
       <c r="K9" s="5"/>
       <c r="L9" s="17" t="s">
@@ -1474,31 +1492,31 @@
       <c r="B10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="51">
-        <v>533</v>
-      </c>
-      <c r="D10" s="51">
-        <v>633</v>
-      </c>
-      <c r="E10" s="51">
-        <v>100</v>
-      </c>
-      <c r="F10" s="7">
+      <c r="C10" s="62">
+        <v>-430</v>
+      </c>
+      <c r="D10" s="63">
+        <v>488</v>
+      </c>
+      <c r="E10" s="63">
+        <v>918</v>
+      </c>
+      <c r="F10" s="51">
         <f t="shared" si="0"/>
-        <v>0.19740740740740742</v>
-      </c>
-      <c r="G10" s="51">
-        <v>1824</v>
-      </c>
-      <c r="H10" s="51">
-        <v>1880</v>
-      </c>
-      <c r="I10" s="51">
-        <v>56</v>
+        <v>-0.15925925925925927</v>
+      </c>
+      <c r="G10" s="63">
+        <v>1658</v>
+      </c>
+      <c r="H10" s="63">
+        <v>1747</v>
+      </c>
+      <c r="I10" s="63">
+        <v>89</v>
       </c>
       <c r="J10" s="7">
         <f t="shared" si="1"/>
-        <v>0.6495726495726496</v>
+        <v>0.59045584045584043</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="17" t="s">
@@ -1522,31 +1540,31 @@
       <c r="B11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="51">
-        <v>317</v>
-      </c>
-      <c r="D11" s="51">
-        <v>423</v>
-      </c>
-      <c r="E11" s="51">
-        <v>106</v>
+      <c r="C11" s="63">
+        <v>235</v>
+      </c>
+      <c r="D11" s="63">
+        <v>316</v>
+      </c>
+      <c r="E11" s="63">
+        <v>81</v>
       </c>
       <c r="F11" s="7">
         <f t="shared" si="0"/>
-        <v>0.32020202020202021</v>
-      </c>
-      <c r="G11" s="51">
+        <v>0.23737373737373738</v>
+      </c>
+      <c r="G11" s="63">
+        <v>953</v>
+      </c>
+      <c r="H11" s="63">
         <v>975</v>
       </c>
-      <c r="H11" s="51">
-        <v>982</v>
-      </c>
-      <c r="I11" s="51">
-        <v>7</v>
+      <c r="I11" s="63">
+        <v>22</v>
       </c>
       <c r="J11" s="7">
         <f t="shared" si="1"/>
-        <v>0.94696969696969702</v>
+        <v>0.92560217560217573</v>
       </c>
       <c r="K11" s="5"/>
       <c r="L11" s="16" t="s">
@@ -1572,31 +1590,31 @@
       <c r="B12" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="52">
-        <v>1734</v>
-      </c>
-      <c r="D12" s="52">
-        <v>2167</v>
-      </c>
-      <c r="E12" s="52">
-        <v>433</v>
-      </c>
-      <c r="F12" s="50">
+      <c r="C12" s="64">
+        <v>-404</v>
+      </c>
+      <c r="D12" s="65">
+        <v>1488</v>
+      </c>
+      <c r="E12" s="65">
+        <v>1892</v>
+      </c>
+      <c r="F12" s="66">
         <f>C12/C67</f>
-        <v>0.15616345829111786</v>
-      </c>
-      <c r="G12" s="52">
-        <v>6938</v>
-      </c>
-      <c r="H12" s="52">
-        <v>7279</v>
-      </c>
-      <c r="I12" s="52">
-        <v>341</v>
+        <v>-3.6384104469210851E-2</v>
+      </c>
+      <c r="G12" s="65">
+        <v>6105</v>
+      </c>
+      <c r="H12" s="65">
+        <v>6597</v>
+      </c>
+      <c r="I12" s="65">
+        <v>492</v>
       </c>
       <c r="J12" s="50">
         <f t="shared" si="1"/>
-        <v>0.60080187739762214</v>
+        <v>0.52866754994414566</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="17" t="s">
@@ -1622,24 +1640,24 @@
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="54"/>
-      <c r="B13" s="55"/>
-      <c r="C13" s="56" t="s">
+      <c r="A13" s="52"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="55"/>
-      <c r="E13" s="56">
+      <c r="D13" s="53"/>
+      <c r="E13" s="54">
         <v>25</v>
       </c>
-      <c r="F13" s="55"/>
-      <c r="G13" s="56" t="s">
+      <c r="F13" s="53"/>
+      <c r="G13" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="55"/>
-      <c r="I13" s="56">
+      <c r="H13" s="53"/>
+      <c r="I13" s="54">
         <v>26</v>
       </c>
-      <c r="J13" s="55"/>
+      <c r="J13" s="53"/>
       <c r="K13" s="5"/>
       <c r="L13" s="17" t="s">
         <v>19</v>

--- a/template.xlsx
+++ b/template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\1. Work\1. Daily\Capacity Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166C5124-C16E-4E02-99CA-0B0B7628DF51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABF7B9FE-6D89-48B7-9D90-84387C24D915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="810" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -396,10 +396,10 @@
     <t>Available Capacity (First)</t>
   </si>
   <si>
-    <t>August</t>
-  </si>
-  <si>
     <t>September</t>
+  </si>
+  <si>
+    <t>October</t>
   </si>
 </sst>
 </file>
@@ -487,13 +487,13 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -696,7 +696,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -765,11 +765,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -778,6 +773,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -785,11 +781,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="3" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="15" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1111,18 +1109,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
+      <c r="A1" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
       <c r="K1" s="5"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1150,24 +1148,24 @@
       <c r="R2" s="15"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="60" t="s">
+      <c r="A3" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="B3" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="57" t="s">
+      <c r="C3" s="54" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="59" t="s">
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="57" t="s">
         <v>119</v>
       </c>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="53"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="56"/>
       <c r="K3" s="5"/>
       <c r="L3" s="16" t="s">
         <v>5</v>
@@ -1192,15 +1190,15 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="61"/>
-      <c r="B4" s="61"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="59"/>
       <c r="C4" s="48">
         <f ca="1">TODAY()</f>
-        <v>46235</v>
+        <v>46257</v>
       </c>
       <c r="D4" s="48">
         <f ca="1">C4-1</f>
-        <v>46234</v>
+        <v>46256</v>
       </c>
       <c r="E4" s="49" t="s">
         <v>12</v>
@@ -1210,11 +1208,11 @@
       </c>
       <c r="G4" s="48">
         <f ca="1">C4</f>
-        <v>46235</v>
+        <v>46257</v>
       </c>
       <c r="H4" s="48">
         <f ca="1">D4</f>
-        <v>46234</v>
+        <v>46256</v>
       </c>
       <c r="I4" s="49" t="s">
         <v>12</v>
@@ -1245,30 +1243,30 @@
         <v>17</v>
       </c>
       <c r="C5" s="62">
-        <v>-25</v>
+        <v>51</v>
       </c>
       <c r="D5" s="62">
-        <v>-63</v>
+        <v>55</v>
       </c>
       <c r="E5" s="62">
-        <v>-38</v>
-      </c>
-      <c r="F5" s="51">
+        <v>4</v>
+      </c>
+      <c r="F5" s="7">
         <f>C5/C60</f>
-        <v>-1.4925373134328358E-2</v>
-      </c>
-      <c r="G5" s="63">
-        <v>1311</v>
-      </c>
-      <c r="H5" s="63">
-        <v>1409</v>
-      </c>
-      <c r="I5" s="63">
-        <v>98</v>
+        <v>2.9276693455797934E-2</v>
+      </c>
+      <c r="G5" s="62">
+        <v>1305</v>
+      </c>
+      <c r="H5" s="62">
+        <v>1310</v>
+      </c>
+      <c r="I5" s="62">
+        <v>5</v>
       </c>
       <c r="J5" s="7">
         <f>G5/D60</f>
-        <v>0.7525832376578645</v>
+        <v>0.74913892078071187</v>
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="17" t="s">
@@ -1295,30 +1293,30 @@
         <v>17</v>
       </c>
       <c r="C6" s="62">
-        <v>-16</v>
-      </c>
-      <c r="D6" s="63">
-        <v>129</v>
+        <v>360</v>
+      </c>
+      <c r="D6" s="62">
+        <v>358</v>
       </c>
       <c r="E6" s="63">
-        <v>145</v>
-      </c>
-      <c r="F6" s="51">
+        <v>-2</v>
+      </c>
+      <c r="F6" s="7">
         <f t="shared" ref="F6:F11" si="0">C6/C61</f>
-        <v>-2.1052631578947368E-2</v>
-      </c>
-      <c r="G6" s="63">
-        <v>396</v>
-      </c>
-      <c r="H6" s="63">
-        <v>426</v>
+        <v>0.45546558704453444</v>
+      </c>
+      <c r="G6" s="62">
+        <v>69</v>
+      </c>
+      <c r="H6" s="62">
+        <v>63</v>
       </c>
       <c r="I6" s="63">
-        <v>30</v>
+        <v>-6</v>
       </c>
       <c r="J6" s="7">
         <f t="shared" ref="J6:J12" si="1">G6/D61</f>
-        <v>0.50101214574898789</v>
+        <v>8.7297570850202427E-2</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="17" t="s">
@@ -1343,30 +1341,30 @@
         <v>17</v>
       </c>
       <c r="C7" s="62">
-        <v>-194</v>
-      </c>
-      <c r="D7" s="63">
-        <v>412</v>
-      </c>
-      <c r="E7" s="63">
-        <v>606</v>
-      </c>
-      <c r="F7" s="51">
+        <v>11</v>
+      </c>
+      <c r="D7" s="62">
+        <v>19</v>
+      </c>
+      <c r="E7" s="62">
+        <v>8</v>
+      </c>
+      <c r="F7" s="7">
         <f t="shared" si="0"/>
-        <v>-0.10203813280736358</v>
-      </c>
-      <c r="G7" s="63">
-        <v>727</v>
-      </c>
-      <c r="H7" s="63">
-        <v>782</v>
-      </c>
-      <c r="I7" s="63">
-        <v>55</v>
+        <v>5.5631416578162144E-3</v>
+      </c>
+      <c r="G7" s="62">
+        <v>865</v>
+      </c>
+      <c r="H7" s="62">
+        <v>889</v>
+      </c>
+      <c r="I7" s="62">
+        <v>24</v>
       </c>
       <c r="J7" s="7">
         <f t="shared" si="1"/>
-        <v>0.36767308956658068</v>
+        <v>0.43746523036463864</v>
       </c>
       <c r="K7" s="5"/>
       <c r="L7" s="16" t="s">
@@ -1392,31 +1390,31 @@
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="62">
-        <v>-62</v>
-      </c>
-      <c r="D8" s="62">
-        <v>-31</v>
+      <c r="C8" s="63">
+        <v>-150</v>
+      </c>
+      <c r="D8" s="63">
+        <v>-163</v>
       </c>
       <c r="E8" s="63">
-        <v>31</v>
+        <v>-13</v>
       </c>
       <c r="F8" s="51">
         <f t="shared" si="0"/>
-        <v>-3.9616613418530351E-2</v>
-      </c>
-      <c r="G8" s="62">
-        <v>-117</v>
+        <v>-9.2160235930203976E-2</v>
+      </c>
+      <c r="G8" s="63">
+        <v>-48</v>
       </c>
       <c r="H8" s="62">
-        <v>-100</v>
-      </c>
-      <c r="I8" s="63">
-        <v>17</v>
+        <v>28</v>
+      </c>
+      <c r="I8" s="62">
+        <v>76</v>
       </c>
       <c r="J8" s="51">
         <f t="shared" si="1"/>
-        <v>-7.1884984025559109E-2</v>
+        <v>-2.9491275497665274E-2</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="17" t="s">
@@ -1442,31 +1440,31 @@
       <c r="B9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="63">
-        <v>89</v>
-      </c>
-      <c r="D9" s="63">
-        <v>236</v>
-      </c>
-      <c r="E9" s="63">
-        <v>147</v>
+      <c r="C9" s="62">
+        <v>237</v>
+      </c>
+      <c r="D9" s="62">
+        <v>250</v>
+      </c>
+      <c r="E9" s="62">
+        <v>13</v>
       </c>
       <c r="F9" s="7">
         <f t="shared" si="0"/>
-        <v>5.8842975206611567E-2</v>
-      </c>
-      <c r="G9" s="63">
-        <v>1176</v>
-      </c>
-      <c r="H9" s="63">
-        <v>1358</v>
-      </c>
-      <c r="I9" s="63">
-        <v>182</v>
+        <v>0.15066751430387795</v>
+      </c>
+      <c r="G9" s="62">
+        <v>1482</v>
+      </c>
+      <c r="H9" s="62">
+        <v>1516</v>
+      </c>
+      <c r="I9" s="62">
+        <v>34</v>
       </c>
       <c r="J9" s="7">
         <f t="shared" si="1"/>
-        <v>0.74761602034329311</v>
+        <v>0.94214876033057848</v>
       </c>
       <c r="K9" s="5"/>
       <c r="L9" s="17" t="s">
@@ -1493,30 +1491,30 @@
         <v>17</v>
       </c>
       <c r="C10" s="62">
-        <v>-430</v>
-      </c>
-      <c r="D10" s="63">
-        <v>488</v>
+        <v>218</v>
+      </c>
+      <c r="D10" s="62">
+        <v>214</v>
       </c>
       <c r="E10" s="63">
-        <v>918</v>
-      </c>
-      <c r="F10" s="51">
+        <v>-4</v>
+      </c>
+      <c r="F10" s="7">
         <f t="shared" si="0"/>
-        <v>-0.15925925925925927</v>
-      </c>
-      <c r="G10" s="63">
-        <v>1658</v>
-      </c>
-      <c r="H10" s="63">
-        <v>1747</v>
-      </c>
-      <c r="I10" s="63">
-        <v>89</v>
+        <v>7.7635327635327642E-2</v>
+      </c>
+      <c r="G10" s="62">
+        <v>2105</v>
+      </c>
+      <c r="H10" s="62">
+        <v>2131</v>
+      </c>
+      <c r="I10" s="62">
+        <v>26</v>
       </c>
       <c r="J10" s="7">
         <f t="shared" si="1"/>
-        <v>0.59045584045584043</v>
+        <v>0.74964387464387461</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="17" t="s">
@@ -1540,31 +1538,31 @@
       <c r="B11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="63">
-        <v>235</v>
-      </c>
-      <c r="D11" s="63">
-        <v>316</v>
-      </c>
-      <c r="E11" s="63">
-        <v>81</v>
+      <c r="C11" s="62">
+        <v>416</v>
+      </c>
+      <c r="D11" s="62">
+        <v>416</v>
+      </c>
+      <c r="E11" s="62">
+        <v>0</v>
       </c>
       <c r="F11" s="7">
         <f t="shared" si="0"/>
-        <v>0.23737373737373738</v>
-      </c>
-      <c r="G11" s="63">
-        <v>953</v>
-      </c>
-      <c r="H11" s="63">
-        <v>975</v>
+        <v>0.40404040404040398</v>
+      </c>
+      <c r="G11" s="62">
+        <v>963</v>
+      </c>
+      <c r="H11" s="62">
+        <v>962</v>
       </c>
       <c r="I11" s="63">
-        <v>22</v>
+        <v>-1</v>
       </c>
       <c r="J11" s="7">
         <f t="shared" si="1"/>
-        <v>0.92560217560217573</v>
+        <v>0.93531468531468542</v>
       </c>
       <c r="K11" s="5"/>
       <c r="L11" s="16" t="s">
@@ -1591,30 +1589,30 @@
         <v>17</v>
       </c>
       <c r="C12" s="64">
-        <v>-404</v>
-      </c>
-      <c r="D12" s="65">
-        <v>1488</v>
-      </c>
-      <c r="E12" s="65">
-        <v>1892</v>
-      </c>
-      <c r="F12" s="66">
+        <v>1142</v>
+      </c>
+      <c r="D12" s="64">
+        <v>1150</v>
+      </c>
+      <c r="E12" s="64">
+        <v>8</v>
+      </c>
+      <c r="F12" s="50">
         <f>C12/C67</f>
-        <v>-3.6384104469210851E-2</v>
-      </c>
-      <c r="G12" s="65">
-        <v>6105</v>
-      </c>
-      <c r="H12" s="65">
-        <v>6597</v>
-      </c>
-      <c r="I12" s="65">
-        <v>492</v>
+        <v>9.8892439317971231E-2</v>
+      </c>
+      <c r="G12" s="64">
+        <v>6742</v>
+      </c>
+      <c r="H12" s="64">
+        <v>6899</v>
+      </c>
+      <c r="I12" s="64">
+        <v>157</v>
       </c>
       <c r="J12" s="50">
         <f t="shared" si="1"/>
-        <v>0.52866754994414566</v>
+        <v>0.5838290944673924</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="17" t="s">
@@ -1640,24 +1638,24 @@
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="52"/>
-      <c r="B13" s="53"/>
-      <c r="C13" s="54" t="s">
+      <c r="A13" s="60"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="53"/>
-      <c r="E13" s="54">
-        <v>25</v>
-      </c>
-      <c r="F13" s="53"/>
-      <c r="G13" s="54" t="s">
+      <c r="D13" s="56"/>
+      <c r="E13" s="61">
+        <v>26</v>
+      </c>
+      <c r="F13" s="56"/>
+      <c r="G13" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="53"/>
-      <c r="I13" s="54">
+      <c r="H13" s="56"/>
+      <c r="I13" s="61">
         <v>26</v>
       </c>
-      <c r="J13" s="53"/>
+      <c r="J13" s="56"/>
       <c r="K13" s="5"/>
       <c r="L13" s="17" t="s">
         <v>19</v>
@@ -3171,7 +3169,7 @@
       </c>
       <c r="C60" s="5">
         <f>(B60/20)*$E$13</f>
-        <v>1675</v>
+        <v>1742</v>
       </c>
       <c r="D60" s="5">
         <f t="shared" ref="D60:D67" si="2">B60*$I$13/20</f>
@@ -3194,7 +3192,7 @@
       </c>
       <c r="C61" s="5">
         <f t="shared" ref="C61:C67" si="3">(B61/20)*$E$13</f>
-        <v>760</v>
+        <v>790.4</v>
       </c>
       <c r="D61" s="5">
         <f t="shared" si="2"/>
@@ -3217,7 +3215,7 @@
       </c>
       <c r="C62" s="5">
         <f t="shared" si="3"/>
-        <v>1901.25</v>
+        <v>1977.3</v>
       </c>
       <c r="D62" s="5">
         <f t="shared" si="2"/>
@@ -3240,7 +3238,7 @@
       </c>
       <c r="C63" s="5">
         <f t="shared" si="3"/>
-        <v>1565</v>
+        <v>1627.6000000000001</v>
       </c>
       <c r="D63" s="5">
         <f t="shared" si="2"/>
@@ -3263,7 +3261,7 @@
       </c>
       <c r="C64" s="5">
         <f t="shared" si="3"/>
-        <v>1512.5</v>
+        <v>1573</v>
       </c>
       <c r="D64" s="5">
         <f t="shared" si="2"/>
@@ -3286,7 +3284,7 @@
       </c>
       <c r="C65" s="5">
         <f t="shared" si="3"/>
-        <v>2700</v>
+        <v>2808</v>
       </c>
       <c r="D65" s="5">
         <f t="shared" si="2"/>
@@ -3309,7 +3307,7 @@
       </c>
       <c r="C66" s="5">
         <f t="shared" si="3"/>
-        <v>990</v>
+        <v>1029.6000000000001</v>
       </c>
       <c r="D66" s="5">
         <f t="shared" si="2"/>
@@ -3332,7 +3330,7 @@
       </c>
       <c r="C67" s="5">
         <f t="shared" si="3"/>
-        <v>11103.75</v>
+        <v>11547.9</v>
       </c>
       <c r="D67" s="5">
         <f t="shared" si="2"/>
@@ -3395,16 +3393,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="G13:H13"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="G3:J3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="G13:H13"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="51" fitToHeight="0" orientation="landscape" r:id="rId1"/>
